--- a/output/version3/test/25-15/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1357</v>
+        <v>1096</v>
       </c>
       <c r="C2" t="n">
-        <v>1512</v>
+        <v>1187</v>
       </c>
       <c r="D2" t="n">
-        <v>1458</v>
+        <v>1024</v>
       </c>
       <c r="E2" t="n">
-        <v>1538</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="n">
-        <v>1150</v>
+        <v>1048</v>
       </c>
       <c r="G2" t="n">
-        <v>1515</v>
+        <v>1182</v>
       </c>
       <c r="H2" t="n">
-        <v>1340</v>
+        <v>1249</v>
       </c>
       <c r="I2" t="n">
-        <v>1123</v>
+        <v>1283</v>
       </c>
       <c r="J2" t="n">
-        <v>1503</v>
+        <v>1233</v>
       </c>
       <c r="K2" t="n">
-        <v>1242</v>
+        <v>1155</v>
       </c>
       <c r="L2" t="n">
-        <v>1373.8</v>
+        <v>1190.2</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1116</v>
+        <v>1341</v>
       </c>
       <c r="C3" t="n">
-        <v>1333</v>
+        <v>1173</v>
       </c>
       <c r="D3" t="n">
-        <v>1315</v>
+        <v>1517</v>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>1152</v>
       </c>
       <c r="F3" t="n">
-        <v>1363</v>
+        <v>1179</v>
       </c>
       <c r="G3" t="n">
-        <v>1154</v>
+        <v>1292</v>
       </c>
       <c r="H3" t="n">
-        <v>1141</v>
+        <v>1171</v>
       </c>
       <c r="I3" t="n">
-        <v>1341</v>
+        <v>1101</v>
       </c>
       <c r="J3" t="n">
-        <v>1183</v>
+        <v>1136</v>
       </c>
       <c r="K3" t="n">
-        <v>1382</v>
+        <v>1100</v>
       </c>
       <c r="L3" t="n">
-        <v>1269.1</v>
+        <v>1216.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>1039</v>
       </c>
       <c r="C4" t="n">
-        <v>1242</v>
+        <v>1132</v>
       </c>
       <c r="D4" t="n">
-        <v>1269</v>
+        <v>1246</v>
       </c>
       <c r="E4" t="n">
-        <v>1352</v>
+        <v>1136</v>
       </c>
       <c r="F4" t="n">
-        <v>1188</v>
+        <v>1135</v>
       </c>
       <c r="G4" t="n">
-        <v>1103</v>
+        <v>1147</v>
       </c>
       <c r="H4" t="n">
-        <v>1228</v>
+        <v>1074</v>
       </c>
       <c r="I4" t="n">
-        <v>1462</v>
+        <v>1137</v>
       </c>
       <c r="J4" t="n">
-        <v>1093</v>
+        <v>1250</v>
       </c>
       <c r="K4" t="n">
-        <v>1469</v>
+        <v>1004</v>
       </c>
       <c r="L4" t="n">
-        <v>1254.6</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1167</v>
+        <v>943</v>
       </c>
       <c r="C5" t="n">
-        <v>1245</v>
+        <v>906</v>
       </c>
       <c r="D5" t="n">
-        <v>1070</v>
+        <v>1025</v>
       </c>
       <c r="E5" t="n">
-        <v>1187</v>
+        <v>997</v>
       </c>
       <c r="F5" t="n">
-        <v>1208</v>
+        <v>937</v>
       </c>
       <c r="G5" t="n">
-        <v>986</v>
+        <v>1049</v>
       </c>
       <c r="H5" t="n">
-        <v>1422</v>
+        <v>906</v>
       </c>
       <c r="I5" t="n">
-        <v>1190</v>
+        <v>971</v>
       </c>
       <c r="J5" t="n">
-        <v>1101</v>
+        <v>946</v>
       </c>
       <c r="K5" t="n">
-        <v>1145</v>
+        <v>985</v>
       </c>
       <c r="L5" t="n">
-        <v>1172.1</v>
+        <v>966.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1201</v>
+        <v>1013</v>
       </c>
       <c r="C6" t="n">
-        <v>1434</v>
+        <v>1124</v>
       </c>
       <c r="D6" t="n">
-        <v>1181</v>
+        <v>1049</v>
       </c>
       <c r="E6" t="n">
-        <v>1347</v>
+        <v>1026</v>
       </c>
       <c r="F6" t="n">
-        <v>1155</v>
+        <v>1225</v>
       </c>
       <c r="G6" t="n">
-        <v>1249</v>
+        <v>1094</v>
       </c>
       <c r="H6" t="n">
-        <v>1377</v>
+        <v>1247</v>
       </c>
       <c r="I6" t="n">
-        <v>1368</v>
+        <v>1049</v>
       </c>
       <c r="J6" t="n">
-        <v>1119</v>
+        <v>1040</v>
       </c>
       <c r="K6" t="n">
-        <v>1359</v>
+        <v>1214</v>
       </c>
       <c r="L6" t="n">
-        <v>1279</v>
+        <v>1108.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1053</v>
+        <v>1177</v>
       </c>
       <c r="C7" t="n">
-        <v>1129</v>
+        <v>1216</v>
       </c>
       <c r="D7" t="n">
-        <v>1070</v>
+        <v>1020</v>
       </c>
       <c r="E7" t="n">
-        <v>1084</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="G7" t="n">
-        <v>1343</v>
+        <v>998</v>
       </c>
       <c r="H7" t="n">
-        <v>1148</v>
+        <v>936</v>
       </c>
       <c r="I7" t="n">
-        <v>1118</v>
+        <v>984</v>
       </c>
       <c r="J7" t="n">
-        <v>1132</v>
+        <v>967</v>
       </c>
       <c r="K7" t="n">
-        <v>1109</v>
+        <v>977</v>
       </c>
       <c r="L7" t="n">
-        <v>1143.6</v>
+        <v>1022.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1347</v>
+        <v>1188</v>
       </c>
       <c r="C8" t="n">
-        <v>1235</v>
+        <v>1445</v>
       </c>
       <c r="D8" t="n">
-        <v>1159</v>
+        <v>1298</v>
       </c>
       <c r="E8" t="n">
-        <v>1158</v>
+        <v>1100</v>
       </c>
       <c r="F8" t="n">
-        <v>1139</v>
+        <v>1069</v>
       </c>
       <c r="G8" t="n">
-        <v>1171</v>
+        <v>1039</v>
       </c>
       <c r="H8" t="n">
-        <v>1018</v>
+        <v>1113</v>
       </c>
       <c r="I8" t="n">
-        <v>1175</v>
+        <v>1049</v>
       </c>
       <c r="J8" t="n">
-        <v>1182</v>
+        <v>988</v>
       </c>
       <c r="K8" t="n">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="L8" t="n">
-        <v>1165.4</v>
+        <v>1135.7</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1285</v>
+        <v>976</v>
       </c>
       <c r="C9" t="n">
-        <v>1287</v>
+        <v>985</v>
       </c>
       <c r="D9" t="n">
-        <v>1229</v>
+        <v>949</v>
       </c>
       <c r="E9" t="n">
-        <v>1100</v>
+        <v>954</v>
       </c>
       <c r="F9" t="n">
-        <v>1230</v>
+        <v>1007</v>
       </c>
       <c r="G9" t="n">
-        <v>1082</v>
+        <v>967</v>
       </c>
       <c r="H9" t="n">
-        <v>1171</v>
+        <v>1065</v>
       </c>
       <c r="I9" t="n">
-        <v>1260</v>
+        <v>1113</v>
       </c>
       <c r="J9" t="n">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="K9" t="n">
-        <v>1152</v>
+        <v>1006</v>
       </c>
       <c r="L9" t="n">
-        <v>1184.1</v>
+        <v>1008.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1241</v>
+        <v>1337</v>
       </c>
       <c r="C10" t="n">
-        <v>1432</v>
+        <v>1106</v>
       </c>
       <c r="D10" t="n">
-        <v>1252</v>
+        <v>1000</v>
       </c>
       <c r="E10" t="n">
-        <v>1089</v>
+        <v>1015</v>
       </c>
       <c r="F10" t="n">
-        <v>1175</v>
+        <v>991</v>
       </c>
       <c r="G10" t="n">
-        <v>1435</v>
+        <v>1049</v>
       </c>
       <c r="H10" t="n">
-        <v>1237</v>
+        <v>1052</v>
       </c>
       <c r="I10" t="n">
-        <v>1310</v>
+        <v>1062</v>
       </c>
       <c r="J10" t="n">
-        <v>1232</v>
+        <v>1077</v>
       </c>
       <c r="K10" t="n">
-        <v>1329</v>
+        <v>1031</v>
       </c>
       <c r="L10" t="n">
-        <v>1273.2</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1404</v>
+        <v>1108</v>
       </c>
       <c r="C11" t="n">
-        <v>1339</v>
+        <v>1138</v>
       </c>
       <c r="D11" t="n">
-        <v>1496</v>
+        <v>1161</v>
       </c>
       <c r="E11" t="n">
-        <v>1169</v>
+        <v>1085</v>
       </c>
       <c r="F11" t="n">
-        <v>1181</v>
+        <v>1320</v>
       </c>
       <c r="G11" t="n">
-        <v>1204</v>
+        <v>1126</v>
       </c>
       <c r="H11" t="n">
-        <v>1204</v>
+        <v>1023</v>
       </c>
       <c r="I11" t="n">
-        <v>1367</v>
+        <v>1163</v>
       </c>
       <c r="J11" t="n">
-        <v>1178</v>
+        <v>1304</v>
       </c>
       <c r="K11" t="n">
-        <v>1168</v>
+        <v>1230</v>
       </c>
       <c r="L11" t="n">
-        <v>1271</v>
+        <v>1165.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1417</v>
+        <v>1157</v>
       </c>
       <c r="C12" t="n">
-        <v>1344</v>
+        <v>1215</v>
       </c>
       <c r="D12" t="n">
-        <v>1242</v>
+        <v>1142</v>
       </c>
       <c r="E12" t="n">
-        <v>1211</v>
+        <v>1117</v>
       </c>
       <c r="F12" t="n">
-        <v>1392</v>
+        <v>1406</v>
       </c>
       <c r="G12" t="n">
-        <v>1388</v>
+        <v>1064</v>
       </c>
       <c r="H12" t="n">
-        <v>1485</v>
+        <v>1191</v>
       </c>
       <c r="I12" t="n">
-        <v>1292</v>
+        <v>1114</v>
       </c>
       <c r="J12" t="n">
-        <v>1372</v>
+        <v>1260</v>
       </c>
       <c r="K12" t="n">
-        <v>1367</v>
+        <v>1187</v>
       </c>
       <c r="L12" t="n">
-        <v>1351</v>
+        <v>1185.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="C13" t="n">
-        <v>1331</v>
+        <v>1081</v>
       </c>
       <c r="D13" t="n">
-        <v>1258</v>
+        <v>1522</v>
       </c>
       <c r="E13" t="n">
-        <v>1420</v>
+        <v>1067</v>
       </c>
       <c r="F13" t="n">
-        <v>1297</v>
+        <v>1158</v>
       </c>
       <c r="G13" t="n">
-        <v>1351</v>
+        <v>1253</v>
       </c>
       <c r="H13" t="n">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="I13" t="n">
-        <v>1358</v>
+        <v>1200</v>
       </c>
       <c r="J13" t="n">
-        <v>1375</v>
+        <v>1189</v>
       </c>
       <c r="K13" t="n">
-        <v>1319</v>
+        <v>1112</v>
       </c>
       <c r="L13" t="n">
-        <v>1323.7</v>
+        <v>1212.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1446</v>
+        <v>1097</v>
       </c>
       <c r="C14" t="n">
-        <v>1165</v>
+        <v>999</v>
       </c>
       <c r="D14" t="n">
-        <v>1017</v>
+        <v>1094</v>
       </c>
       <c r="E14" t="n">
-        <v>1138</v>
+        <v>954</v>
       </c>
       <c r="F14" t="n">
-        <v>1232</v>
+        <v>1007</v>
       </c>
       <c r="G14" t="n">
-        <v>1273</v>
+        <v>1034</v>
       </c>
       <c r="H14" t="n">
-        <v>1330</v>
+        <v>1267</v>
       </c>
       <c r="I14" t="n">
-        <v>1049</v>
+        <v>1214</v>
       </c>
       <c r="J14" t="n">
-        <v>1433</v>
+        <v>905</v>
       </c>
       <c r="K14" t="n">
-        <v>1310</v>
+        <v>936</v>
       </c>
       <c r="L14" t="n">
-        <v>1239.3</v>
+        <v>1050.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1432</v>
+        <v>1001</v>
       </c>
       <c r="C15" t="n">
-        <v>1202</v>
+        <v>1075</v>
       </c>
       <c r="D15" t="n">
-        <v>1517</v>
+        <v>1032</v>
       </c>
       <c r="E15" t="n">
-        <v>1245</v>
+        <v>1101</v>
       </c>
       <c r="F15" t="n">
-        <v>1196</v>
+        <v>1080</v>
       </c>
       <c r="G15" t="n">
-        <v>1298</v>
+        <v>1113</v>
       </c>
       <c r="H15" t="n">
-        <v>1530</v>
+        <v>1075</v>
       </c>
       <c r="I15" t="n">
-        <v>1131</v>
+        <v>1018</v>
       </c>
       <c r="J15" t="n">
-        <v>1168</v>
+        <v>977</v>
       </c>
       <c r="K15" t="n">
-        <v>1438</v>
+        <v>982</v>
       </c>
       <c r="L15" t="n">
-        <v>1315.7</v>
+        <v>1045.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1244</v>
+        <v>1128</v>
       </c>
       <c r="C16" t="n">
-        <v>1202</v>
+        <v>1144</v>
       </c>
       <c r="D16" t="n">
-        <v>1205</v>
+        <v>1057</v>
       </c>
       <c r="E16" t="n">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="F16" t="n">
-        <v>1182</v>
+        <v>1022</v>
       </c>
       <c r="G16" t="n">
-        <v>1249</v>
+        <v>1100</v>
       </c>
       <c r="H16" t="n">
-        <v>1114</v>
+        <v>1210</v>
       </c>
       <c r="I16" t="n">
-        <v>1185</v>
+        <v>1219</v>
       </c>
       <c r="J16" t="n">
-        <v>1204</v>
+        <v>1005</v>
       </c>
       <c r="K16" t="n">
-        <v>1217</v>
+        <v>1184</v>
       </c>
       <c r="L16" t="n">
-        <v>1201.4</v>
+        <v>1128.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1080</v>
+        <v>1035</v>
       </c>
       <c r="C17" t="n">
-        <v>1259</v>
+        <v>1067</v>
       </c>
       <c r="D17" t="n">
-        <v>1173</v>
+        <v>1079</v>
       </c>
       <c r="E17" t="n">
-        <v>1440</v>
+        <v>1116</v>
       </c>
       <c r="F17" t="n">
-        <v>1354</v>
+        <v>1040</v>
       </c>
       <c r="G17" t="n">
-        <v>1212</v>
+        <v>1156</v>
       </c>
       <c r="H17" t="n">
-        <v>1343</v>
+        <v>1161</v>
       </c>
       <c r="I17" t="n">
-        <v>1334</v>
+        <v>969</v>
       </c>
       <c r="J17" t="n">
-        <v>1398</v>
+        <v>1092</v>
       </c>
       <c r="K17" t="n">
-        <v>1367</v>
+        <v>1072</v>
       </c>
       <c r="L17" t="n">
-        <v>1296</v>
+        <v>1078.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1309</v>
+        <v>1076</v>
       </c>
       <c r="C18" t="n">
-        <v>1375</v>
+        <v>1085</v>
       </c>
       <c r="D18" t="n">
-        <v>1104</v>
+        <v>997</v>
       </c>
       <c r="E18" t="n">
-        <v>1319</v>
+        <v>1094</v>
       </c>
       <c r="F18" t="n">
-        <v>1290</v>
+        <v>1069</v>
       </c>
       <c r="G18" t="n">
-        <v>1516</v>
+        <v>1185</v>
       </c>
       <c r="H18" t="n">
-        <v>1245</v>
+        <v>1036</v>
       </c>
       <c r="I18" t="n">
-        <v>1524</v>
+        <v>1034</v>
       </c>
       <c r="J18" t="n">
-        <v>1097</v>
+        <v>1233</v>
       </c>
       <c r="K18" t="n">
-        <v>1215</v>
+        <v>1148</v>
       </c>
       <c r="L18" t="n">
-        <v>1299.4</v>
+        <v>1095.7</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1311</v>
+        <v>1136</v>
       </c>
       <c r="C19" t="n">
-        <v>1333</v>
+        <v>1303</v>
       </c>
       <c r="D19" t="n">
-        <v>1276</v>
+        <v>1205</v>
       </c>
       <c r="E19" t="n">
-        <v>1423</v>
+        <v>1279</v>
       </c>
       <c r="F19" t="n">
-        <v>1320</v>
+        <v>1387</v>
       </c>
       <c r="G19" t="n">
-        <v>1184</v>
+        <v>1097</v>
       </c>
       <c r="H19" t="n">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="I19" t="n">
-        <v>1182</v>
+        <v>1368</v>
       </c>
       <c r="J19" t="n">
-        <v>1246</v>
+        <v>1100</v>
       </c>
       <c r="K19" t="n">
-        <v>1224</v>
+        <v>1206</v>
       </c>
       <c r="L19" t="n">
-        <v>1285.9</v>
+        <v>1245.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1460</v>
+        <v>1253</v>
       </c>
       <c r="C20" t="n">
+        <v>1311</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1277</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1177</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1327</v>
+      </c>
+      <c r="I20" t="n">
         <v>1195</v>
       </c>
-      <c r="D20" t="n">
-        <v>1134</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1396</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1535</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1165</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1395</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1448</v>
-      </c>
       <c r="J20" t="n">
-        <v>1273</v>
+        <v>1177</v>
       </c>
       <c r="K20" t="n">
-        <v>1161</v>
+        <v>1104</v>
       </c>
       <c r="L20" t="n">
-        <v>1316.2</v>
+        <v>1183.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1472</v>
+        <v>1019</v>
       </c>
       <c r="C21" t="n">
-        <v>1321</v>
+        <v>1107</v>
       </c>
       <c r="D21" t="n">
-        <v>1471</v>
+        <v>1278</v>
       </c>
       <c r="E21" t="n">
-        <v>1146</v>
+        <v>1059</v>
       </c>
       <c r="F21" t="n">
-        <v>1366</v>
+        <v>1116</v>
       </c>
       <c r="G21" t="n">
-        <v>1279</v>
+        <v>1166</v>
       </c>
       <c r="H21" t="n">
-        <v>1427</v>
+        <v>1094</v>
       </c>
       <c r="I21" t="n">
-        <v>1450</v>
+        <v>1189</v>
       </c>
       <c r="J21" t="n">
-        <v>1576</v>
+        <v>1148</v>
       </c>
       <c r="K21" t="n">
-        <v>1201</v>
+        <v>1134</v>
       </c>
       <c r="L21" t="n">
-        <v>1370.9</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1276</v>
+        <v>1168</v>
       </c>
       <c r="C22" t="n">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="D22" t="n">
-        <v>1126</v>
+        <v>1251</v>
       </c>
       <c r="E22" t="n">
-        <v>1197</v>
+        <v>1136</v>
       </c>
       <c r="F22" t="n">
-        <v>1084</v>
+        <v>1190</v>
       </c>
       <c r="G22" t="n">
-        <v>1339</v>
+        <v>1179</v>
       </c>
       <c r="H22" t="n">
-        <v>1339</v>
+        <v>1231</v>
       </c>
       <c r="I22" t="n">
-        <v>1289</v>
+        <v>1155</v>
       </c>
       <c r="J22" t="n">
-        <v>1307</v>
+        <v>1152</v>
       </c>
       <c r="K22" t="n">
-        <v>1479</v>
+        <v>1068</v>
       </c>
       <c r="L22" t="n">
-        <v>1258.1</v>
+        <v>1166.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1073</v>
+        <v>1041</v>
       </c>
       <c r="C23" t="n">
-        <v>1363</v>
+        <v>999</v>
       </c>
       <c r="D23" t="n">
-        <v>1074</v>
+        <v>930</v>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>1013</v>
       </c>
       <c r="F23" t="n">
-        <v>1154</v>
+        <v>1119</v>
       </c>
       <c r="G23" t="n">
-        <v>1314</v>
+        <v>927</v>
       </c>
       <c r="H23" t="n">
-        <v>1243</v>
+        <v>916</v>
       </c>
       <c r="I23" t="n">
-        <v>1427</v>
+        <v>1003</v>
       </c>
       <c r="J23" t="n">
-        <v>1415</v>
+        <v>998</v>
       </c>
       <c r="K23" t="n">
-        <v>1092</v>
+        <v>968</v>
       </c>
       <c r="L23" t="n">
-        <v>1225.6</v>
+        <v>991.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1336</v>
+        <v>1094</v>
       </c>
       <c r="C24" t="n">
-        <v>1265</v>
+        <v>1210</v>
       </c>
       <c r="D24" t="n">
-        <v>1288</v>
+        <v>1058</v>
       </c>
       <c r="E24" t="n">
-        <v>1228</v>
+        <v>1087</v>
       </c>
       <c r="F24" t="n">
-        <v>1165</v>
+        <v>1026</v>
       </c>
       <c r="G24" t="n">
-        <v>1552</v>
+        <v>1050</v>
       </c>
       <c r="H24" t="n">
-        <v>1396</v>
+        <v>1017</v>
       </c>
       <c r="I24" t="n">
-        <v>1401</v>
+        <v>1074</v>
       </c>
       <c r="J24" t="n">
-        <v>1264</v>
+        <v>1159</v>
       </c>
       <c r="K24" t="n">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="L24" t="n">
-        <v>1306.7</v>
+        <v>1095.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1251</v>
+        <v>1291</v>
       </c>
       <c r="C25" t="n">
-        <v>1164</v>
+        <v>1120</v>
       </c>
       <c r="D25" t="n">
-        <v>1186</v>
+        <v>1028</v>
       </c>
       <c r="E25" t="n">
-        <v>1241</v>
+        <v>1149</v>
       </c>
       <c r="F25" t="n">
-        <v>1401</v>
+        <v>1193</v>
       </c>
       <c r="G25" t="n">
-        <v>1445</v>
+        <v>1095</v>
       </c>
       <c r="H25" t="n">
-        <v>1215</v>
+        <v>1286</v>
       </c>
       <c r="I25" t="n">
-        <v>1204</v>
+        <v>1126</v>
       </c>
       <c r="J25" t="n">
-        <v>1129</v>
+        <v>1195</v>
       </c>
       <c r="K25" t="n">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="L25" t="n">
-        <v>1245.7</v>
+        <v>1170.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1212</v>
+        <v>1149</v>
       </c>
       <c r="C26" t="n">
-        <v>1266</v>
+        <v>1056</v>
       </c>
       <c r="D26" t="n">
-        <v>1268</v>
+        <v>1077</v>
       </c>
       <c r="E26" t="n">
-        <v>1406</v>
+        <v>1068</v>
       </c>
       <c r="F26" t="n">
-        <v>1173</v>
+        <v>1057</v>
       </c>
       <c r="G26" t="n">
-        <v>1162</v>
+        <v>982</v>
       </c>
       <c r="H26" t="n">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="I26" t="n">
-        <v>1380</v>
+        <v>1114</v>
       </c>
       <c r="J26" t="n">
-        <v>1146</v>
+        <v>1206</v>
       </c>
       <c r="K26" t="n">
-        <v>1261</v>
+        <v>1066</v>
       </c>
       <c r="L26" t="n">
-        <v>1246.5</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1257</v>
+        <v>1049</v>
       </c>
       <c r="C27" t="n">
-        <v>1333</v>
+        <v>1389</v>
       </c>
       <c r="D27" t="n">
-        <v>1343</v>
+        <v>1101</v>
       </c>
       <c r="E27" t="n">
-        <v>1216</v>
+        <v>1129</v>
       </c>
       <c r="F27" t="n">
-        <v>1083</v>
+        <v>1172</v>
       </c>
       <c r="G27" t="n">
-        <v>1225</v>
+        <v>996</v>
       </c>
       <c r="H27" t="n">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="I27" t="n">
-        <v>1217</v>
+        <v>1430</v>
       </c>
       <c r="J27" t="n">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="K27" t="n">
-        <v>1255</v>
+        <v>1048</v>
       </c>
       <c r="L27" t="n">
-        <v>1232.5</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1237</v>
+        <v>1275</v>
       </c>
       <c r="C28" t="n">
-        <v>1178</v>
+        <v>1094</v>
       </c>
       <c r="D28" t="n">
-        <v>1335</v>
+        <v>1063</v>
       </c>
       <c r="E28" t="n">
-        <v>1210</v>
+        <v>1044</v>
       </c>
       <c r="F28" t="n">
-        <v>1098</v>
+        <v>1349</v>
       </c>
       <c r="G28" t="n">
-        <v>1291</v>
+        <v>1099</v>
       </c>
       <c r="H28" t="n">
-        <v>1283</v>
+        <v>1343</v>
       </c>
       <c r="I28" t="n">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="J28" t="n">
-        <v>1277</v>
+        <v>1068</v>
       </c>
       <c r="K28" t="n">
-        <v>1313</v>
+        <v>1125</v>
       </c>
       <c r="L28" t="n">
-        <v>1243</v>
+        <v>1167.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1187</v>
+        <v>1076</v>
       </c>
       <c r="C29" t="n">
-        <v>1450</v>
+        <v>1030</v>
       </c>
       <c r="D29" t="n">
-        <v>1106</v>
+        <v>1066</v>
       </c>
       <c r="E29" t="n">
-        <v>1197</v>
+        <v>1063</v>
       </c>
       <c r="F29" t="n">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="G29" t="n">
-        <v>1229</v>
+        <v>1013</v>
       </c>
       <c r="H29" t="n">
-        <v>1077</v>
+        <v>937</v>
       </c>
       <c r="I29" t="n">
-        <v>1409</v>
+        <v>960</v>
       </c>
       <c r="J29" t="n">
-        <v>1333</v>
+        <v>1095</v>
       </c>
       <c r="K29" t="n">
-        <v>972</v>
+        <v>1030</v>
       </c>
       <c r="L29" t="n">
-        <v>1203</v>
+        <v>1032.8</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1305</v>
+        <v>974</v>
       </c>
       <c r="C30" t="n">
-        <v>1434</v>
+        <v>1004</v>
       </c>
       <c r="D30" t="n">
-        <v>1154</v>
+        <v>1004</v>
       </c>
       <c r="E30" t="n">
-        <v>1309</v>
+        <v>991</v>
       </c>
       <c r="F30" t="n">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="G30" t="n">
-        <v>1320</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1213</v>
+        <v>1153</v>
       </c>
       <c r="I30" t="n">
-        <v>1232</v>
+        <v>1193</v>
       </c>
       <c r="J30" t="n">
-        <v>1219</v>
+        <v>1093</v>
       </c>
       <c r="K30" t="n">
-        <v>1127</v>
+        <v>1084</v>
       </c>
       <c r="L30" t="n">
-        <v>1245.1</v>
+        <v>1062.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1305</v>
+        <v>1099</v>
       </c>
       <c r="C31" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D31" t="n">
-        <v>1384</v>
+        <v>1123</v>
       </c>
       <c r="E31" t="n">
-        <v>1315</v>
+        <v>1168</v>
       </c>
       <c r="F31" t="n">
-        <v>1288</v>
+        <v>1002</v>
       </c>
       <c r="G31" t="n">
-        <v>1389</v>
+        <v>1083</v>
       </c>
       <c r="H31" t="n">
-        <v>1266</v>
+        <v>1124</v>
       </c>
       <c r="I31" t="n">
-        <v>1070</v>
+        <v>1311</v>
       </c>
       <c r="J31" t="n">
-        <v>1390</v>
+        <v>1236</v>
       </c>
       <c r="K31" t="n">
-        <v>1120</v>
+        <v>1203</v>
       </c>
       <c r="L31" t="n">
-        <v>1262.7</v>
+        <v>1143.9</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1241</v>
+        <v>1015</v>
       </c>
       <c r="C32" t="n">
-        <v>1124</v>
+        <v>1006</v>
       </c>
       <c r="D32" t="n">
-        <v>1347</v>
+        <v>1090</v>
       </c>
       <c r="E32" t="n">
-        <v>1271</v>
+        <v>999</v>
       </c>
       <c r="F32" t="n">
-        <v>1089</v>
+        <v>954</v>
       </c>
       <c r="G32" t="n">
-        <v>992</v>
+        <v>958</v>
       </c>
       <c r="H32" t="n">
-        <v>1283</v>
+        <v>990</v>
       </c>
       <c r="I32" t="n">
-        <v>1064</v>
+        <v>1188</v>
       </c>
       <c r="J32" t="n">
-        <v>1077</v>
+        <v>849</v>
       </c>
       <c r="K32" t="n">
-        <v>1007</v>
+        <v>1052</v>
       </c>
       <c r="L32" t="n">
-        <v>1149.5</v>
+        <v>1010.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1391</v>
+        <v>1040</v>
       </c>
       <c r="C33" t="n">
-        <v>1499</v>
+        <v>1106</v>
       </c>
       <c r="D33" t="n">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E33" t="n">
-        <v>1292</v>
+        <v>983</v>
       </c>
       <c r="F33" t="n">
-        <v>1086</v>
+        <v>986</v>
       </c>
       <c r="G33" t="n">
-        <v>1336</v>
+        <v>1217</v>
       </c>
       <c r="H33" t="n">
-        <v>1476</v>
+        <v>1074</v>
       </c>
       <c r="I33" t="n">
-        <v>1334</v>
+        <v>1398</v>
       </c>
       <c r="J33" t="n">
-        <v>1201</v>
+        <v>1087</v>
       </c>
       <c r="K33" t="n">
-        <v>1169</v>
+        <v>1271</v>
       </c>
       <c r="L33" t="n">
-        <v>1294.2</v>
+        <v>1132.2</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1219</v>
+        <v>1136</v>
       </c>
       <c r="C34" t="n">
-        <v>1179</v>
+        <v>1155</v>
       </c>
       <c r="D34" t="n">
-        <v>1104</v>
+        <v>1124</v>
       </c>
       <c r="E34" t="n">
-        <v>1195</v>
+        <v>1103</v>
       </c>
       <c r="F34" t="n">
-        <v>1261</v>
+        <v>1090</v>
       </c>
       <c r="G34" t="n">
-        <v>1202</v>
+        <v>1129</v>
       </c>
       <c r="H34" t="n">
-        <v>1357</v>
+        <v>1163</v>
       </c>
       <c r="I34" t="n">
-        <v>1262</v>
+        <v>1130</v>
       </c>
       <c r="J34" t="n">
-        <v>1188</v>
+        <v>1111</v>
       </c>
       <c r="K34" t="n">
-        <v>1164</v>
+        <v>1107</v>
       </c>
       <c r="L34" t="n">
-        <v>1213.1</v>
+        <v>1124.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1338</v>
+        <v>1158</v>
       </c>
       <c r="C35" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D35" t="n">
+        <v>974</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1119</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1068</v>
+      </c>
+      <c r="I35" t="n">
         <v>1223</v>
       </c>
-      <c r="D35" t="n">
-        <v>1155</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1272</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1272</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1304</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1077</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1268</v>
-      </c>
       <c r="J35" t="n">
-        <v>1273</v>
+        <v>1097</v>
       </c>
       <c r="K35" t="n">
-        <v>1359</v>
+        <v>1003</v>
       </c>
       <c r="L35" t="n">
-        <v>1254.1</v>
+        <v>1095.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1275</v>
+        <v>1126</v>
       </c>
       <c r="C36" t="n">
-        <v>1286</v>
+        <v>1088</v>
       </c>
       <c r="D36" t="n">
-        <v>1129</v>
+        <v>1107</v>
       </c>
       <c r="E36" t="n">
-        <v>1066</v>
+        <v>1148</v>
       </c>
       <c r="F36" t="n">
-        <v>1239</v>
+        <v>1042</v>
       </c>
       <c r="G36" t="n">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="H36" t="n">
-        <v>1184</v>
+        <v>1245</v>
       </c>
       <c r="I36" t="n">
-        <v>1286</v>
+        <v>1094</v>
       </c>
       <c r="J36" t="n">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="K36" t="n">
-        <v>1310</v>
+        <v>1013</v>
       </c>
       <c r="L36" t="n">
-        <v>1189.7</v>
+        <v>1098.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1322</v>
+        <v>989</v>
       </c>
       <c r="C37" t="n">
-        <v>1129</v>
+        <v>984</v>
       </c>
       <c r="D37" t="n">
-        <v>1228</v>
+        <v>1212</v>
       </c>
       <c r="E37" t="n">
-        <v>1172</v>
+        <v>1131</v>
       </c>
       <c r="F37" t="n">
-        <v>1353</v>
+        <v>1170</v>
       </c>
       <c r="G37" t="n">
-        <v>1252</v>
+        <v>1072</v>
       </c>
       <c r="H37" t="n">
-        <v>1179</v>
+        <v>1281</v>
       </c>
       <c r="I37" t="n">
-        <v>1098</v>
+        <v>1049</v>
       </c>
       <c r="J37" t="n">
-        <v>1215</v>
+        <v>1090</v>
       </c>
       <c r="K37" t="n">
-        <v>1112</v>
+        <v>1124</v>
       </c>
       <c r="L37" t="n">
-        <v>1206</v>
+        <v>1110.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="C38" t="n">
-        <v>1200</v>
+        <v>1001</v>
       </c>
       <c r="D38" t="n">
-        <v>1314</v>
+        <v>985</v>
       </c>
       <c r="E38" t="n">
-        <v>1156</v>
+        <v>900</v>
       </c>
       <c r="F38" t="n">
-        <v>1239</v>
+        <v>980</v>
       </c>
       <c r="G38" t="n">
-        <v>1364</v>
+        <v>1052</v>
       </c>
       <c r="H38" t="n">
-        <v>1463</v>
+        <v>1244</v>
       </c>
       <c r="I38" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J38" t="n">
         <v>1048</v>
       </c>
-      <c r="J38" t="n">
-        <v>1187</v>
-      </c>
       <c r="K38" t="n">
-        <v>1065</v>
+        <v>1152</v>
       </c>
       <c r="L38" t="n">
-        <v>1209.9</v>
+        <v>1052.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1083</v>
+        <v>1136</v>
       </c>
       <c r="C39" t="n">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="D39" t="n">
-        <v>1058</v>
+        <v>1028</v>
       </c>
       <c r="E39" t="n">
-        <v>1212</v>
+        <v>1228</v>
       </c>
       <c r="F39" t="n">
-        <v>1194</v>
+        <v>1273</v>
       </c>
       <c r="G39" t="n">
-        <v>1144</v>
+        <v>1168</v>
       </c>
       <c r="H39" t="n">
-        <v>1218</v>
+        <v>1235</v>
       </c>
       <c r="I39" t="n">
-        <v>1071</v>
+        <v>1040</v>
       </c>
       <c r="J39" t="n">
-        <v>1033</v>
+        <v>1245</v>
       </c>
       <c r="K39" t="n">
-        <v>1251</v>
+        <v>1310</v>
       </c>
       <c r="L39" t="n">
-        <v>1139</v>
+        <v>1179.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1422</v>
+        <v>1267</v>
       </c>
       <c r="C40" t="n">
-        <v>1066</v>
+        <v>1226</v>
       </c>
       <c r="D40" t="n">
-        <v>1166</v>
+        <v>1300</v>
       </c>
       <c r="E40" t="n">
-        <v>1494</v>
+        <v>1137</v>
       </c>
       <c r="F40" t="n">
-        <v>1336</v>
+        <v>1004</v>
       </c>
       <c r="G40" t="n">
-        <v>1158</v>
+        <v>1222</v>
       </c>
       <c r="H40" t="n">
-        <v>1429</v>
+        <v>1138</v>
       </c>
       <c r="I40" t="n">
-        <v>1278</v>
+        <v>1146</v>
       </c>
       <c r="J40" t="n">
-        <v>1541</v>
+        <v>1129</v>
       </c>
       <c r="K40" t="n">
-        <v>1174</v>
+        <v>1197</v>
       </c>
       <c r="L40" t="n">
-        <v>1306.4</v>
+        <v>1176.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1427</v>
+        <v>1003</v>
       </c>
       <c r="C41" t="n">
-        <v>1201</v>
+        <v>1100</v>
       </c>
       <c r="D41" t="n">
-        <v>1425</v>
+        <v>1242</v>
       </c>
       <c r="E41" t="n">
-        <v>1283</v>
+        <v>1066</v>
       </c>
       <c r="F41" t="n">
-        <v>1167</v>
+        <v>1261</v>
       </c>
       <c r="G41" t="n">
-        <v>1281</v>
+        <v>1164</v>
       </c>
       <c r="H41" t="n">
-        <v>1169</v>
+        <v>996</v>
       </c>
       <c r="I41" t="n">
-        <v>1220</v>
+        <v>1138</v>
       </c>
       <c r="J41" t="n">
-        <v>1140</v>
+        <v>1040</v>
       </c>
       <c r="K41" t="n">
-        <v>1415</v>
+        <v>1034</v>
       </c>
       <c r="L41" t="n">
-        <v>1272.8</v>
+        <v>1104.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1121</v>
+        <v>1016</v>
       </c>
       <c r="C42" t="n">
-        <v>1085</v>
+        <v>1103</v>
       </c>
       <c r="D42" t="n">
-        <v>1218</v>
+        <v>994</v>
       </c>
       <c r="E42" t="n">
-        <v>1264</v>
+        <v>944</v>
       </c>
       <c r="F42" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="G42" t="n">
-        <v>1297</v>
+        <v>1068</v>
       </c>
       <c r="H42" t="n">
-        <v>1297</v>
+        <v>1061</v>
       </c>
       <c r="I42" t="n">
-        <v>1618</v>
+        <v>1073</v>
       </c>
       <c r="J42" t="n">
-        <v>1164</v>
+        <v>1004</v>
       </c>
       <c r="K42" t="n">
-        <v>1194</v>
+        <v>997</v>
       </c>
       <c r="L42" t="n">
-        <v>1243.3</v>
+        <v>1038.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1483</v>
+        <v>1105</v>
       </c>
       <c r="C43" t="n">
-        <v>1284</v>
+        <v>1269</v>
       </c>
       <c r="D43" t="n">
-        <v>1056</v>
+        <v>1104</v>
       </c>
       <c r="E43" t="n">
-        <v>1244</v>
+        <v>1053</v>
       </c>
       <c r="F43" t="n">
-        <v>1323</v>
+        <v>1179</v>
       </c>
       <c r="G43" t="n">
+        <v>1271</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1012</v>
+      </c>
+      <c r="I43" t="n">
         <v>1102</v>
       </c>
-      <c r="H43" t="n">
-        <v>1202</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1359</v>
-      </c>
       <c r="J43" t="n">
-        <v>1173</v>
+        <v>1139</v>
       </c>
       <c r="K43" t="n">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="L43" t="n">
-        <v>1254.2</v>
+        <v>1155.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1356</v>
+        <v>1026</v>
       </c>
       <c r="C44" t="n">
-        <v>1326</v>
+        <v>1209</v>
       </c>
       <c r="D44" t="n">
-        <v>1209</v>
+        <v>988</v>
       </c>
       <c r="E44" t="n">
-        <v>1385</v>
+        <v>1192</v>
       </c>
       <c r="F44" t="n">
-        <v>1153</v>
+        <v>1025</v>
       </c>
       <c r="G44" t="n">
-        <v>1155</v>
+        <v>1009</v>
       </c>
       <c r="H44" t="n">
-        <v>1212</v>
+        <v>1007</v>
       </c>
       <c r="I44" t="n">
-        <v>1361</v>
+        <v>1067</v>
       </c>
       <c r="J44" t="n">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="K44" t="n">
-        <v>1499</v>
+        <v>1064</v>
       </c>
       <c r="L44" t="n">
-        <v>1285.4</v>
+        <v>1080.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1344</v>
+        <v>1069</v>
       </c>
       <c r="C45" t="n">
-        <v>1339</v>
+        <v>972</v>
       </c>
       <c r="D45" t="n">
-        <v>1047</v>
+        <v>1068</v>
       </c>
       <c r="E45" t="n">
-        <v>1208</v>
+        <v>986</v>
       </c>
       <c r="F45" t="n">
-        <v>1351</v>
+        <v>1013</v>
       </c>
       <c r="G45" t="n">
-        <v>1107</v>
+        <v>1014</v>
       </c>
       <c r="H45" t="n">
-        <v>1285</v>
+        <v>1032</v>
       </c>
       <c r="I45" t="n">
-        <v>1226</v>
+        <v>1168</v>
       </c>
       <c r="J45" t="n">
-        <v>1143</v>
+        <v>1060</v>
       </c>
       <c r="K45" t="n">
-        <v>1187</v>
+        <v>1115</v>
       </c>
       <c r="L45" t="n">
-        <v>1223.7</v>
+        <v>1049.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1242</v>
+        <v>1219</v>
       </c>
       <c r="C46" t="n">
-        <v>1228</v>
+        <v>1152</v>
       </c>
       <c r="D46" t="n">
-        <v>1084</v>
+        <v>1236</v>
       </c>
       <c r="E46" t="n">
-        <v>1362</v>
+        <v>1104</v>
       </c>
       <c r="F46" t="n">
-        <v>1274</v>
+        <v>1122</v>
       </c>
       <c r="G46" t="n">
-        <v>1219</v>
+        <v>1127</v>
       </c>
       <c r="H46" t="n">
-        <v>1164</v>
+        <v>1267</v>
       </c>
       <c r="I46" t="n">
-        <v>1391</v>
+        <v>1153</v>
       </c>
       <c r="J46" t="n">
-        <v>1238</v>
+        <v>1095</v>
       </c>
       <c r="K46" t="n">
-        <v>1084</v>
+        <v>1122</v>
       </c>
       <c r="L46" t="n">
-        <v>1228.6</v>
+        <v>1159.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1488</v>
+        <v>1117</v>
       </c>
       <c r="C47" t="n">
-        <v>1416</v>
+        <v>999</v>
       </c>
       <c r="D47" t="n">
-        <v>1493</v>
+        <v>1121</v>
       </c>
       <c r="E47" t="n">
-        <v>1486</v>
+        <v>1153</v>
       </c>
       <c r="F47" t="n">
-        <v>1468</v>
+        <v>1216</v>
       </c>
       <c r="G47" t="n">
-        <v>1286</v>
+        <v>1135</v>
       </c>
       <c r="H47" t="n">
-        <v>1232</v>
+        <v>1130</v>
       </c>
       <c r="I47" t="n">
-        <v>1563</v>
+        <v>1126</v>
       </c>
       <c r="J47" t="n">
-        <v>1215</v>
+        <v>1085</v>
       </c>
       <c r="K47" t="n">
-        <v>1369</v>
+        <v>1160</v>
       </c>
       <c r="L47" t="n">
-        <v>1401.6</v>
+        <v>1124.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1324</v>
+        <v>1127</v>
       </c>
       <c r="C48" t="n">
-        <v>1145</v>
+        <v>1085</v>
       </c>
       <c r="D48" t="n">
-        <v>1224</v>
+        <v>1034</v>
       </c>
       <c r="E48" t="n">
-        <v>1271</v>
+        <v>1164</v>
       </c>
       <c r="F48" t="n">
-        <v>1136</v>
+        <v>1110</v>
       </c>
       <c r="G48" t="n">
-        <v>1322</v>
+        <v>1108</v>
       </c>
       <c r="H48" t="n">
-        <v>1210</v>
+        <v>1246</v>
       </c>
       <c r="I48" t="n">
-        <v>1412</v>
+        <v>1179</v>
       </c>
       <c r="J48" t="n">
-        <v>1172</v>
+        <v>1186</v>
       </c>
       <c r="K48" t="n">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="L48" t="n">
-        <v>1242</v>
+        <v>1146.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1532</v>
+        <v>1057</v>
       </c>
       <c r="C49" t="n">
-        <v>1363</v>
+        <v>1064</v>
       </c>
       <c r="D49" t="n">
-        <v>1425</v>
+        <v>1080</v>
       </c>
       <c r="E49" t="n">
-        <v>1317</v>
+        <v>1083</v>
       </c>
       <c r="F49" t="n">
-        <v>1277</v>
+        <v>1094</v>
       </c>
       <c r="G49" t="n">
-        <v>1275</v>
+        <v>1115</v>
       </c>
       <c r="H49" t="n">
-        <v>1157</v>
+        <v>1101</v>
       </c>
       <c r="I49" t="n">
-        <v>1336</v>
+        <v>1212</v>
       </c>
       <c r="J49" t="n">
-        <v>1231</v>
+        <v>962</v>
       </c>
       <c r="K49" t="n">
-        <v>1207</v>
+        <v>1056</v>
       </c>
       <c r="L49" t="n">
-        <v>1312</v>
+        <v>1082.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1116</v>
+        <v>1055</v>
       </c>
       <c r="C50" t="n">
-        <v>1378</v>
+        <v>1042</v>
       </c>
       <c r="D50" t="n">
-        <v>1106</v>
+        <v>1046</v>
       </c>
       <c r="E50" t="n">
-        <v>1101</v>
+        <v>1000</v>
       </c>
       <c r="F50" t="n">
-        <v>1117</v>
+        <v>1150</v>
       </c>
       <c r="G50" t="n">
-        <v>1043</v>
+        <v>1122</v>
       </c>
       <c r="H50" t="n">
-        <v>1181</v>
+        <v>1094</v>
       </c>
       <c r="I50" t="n">
-        <v>1161</v>
+        <v>1001</v>
       </c>
       <c r="J50" t="n">
         <v>1089</v>
       </c>
       <c r="K50" t="n">
-        <v>1139</v>
+        <v>1266</v>
       </c>
       <c r="L50" t="n">
-        <v>1143.1</v>
+        <v>1086.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1201</v>
+        <v>1069</v>
       </c>
       <c r="C51" t="n">
-        <v>1311</v>
+        <v>1026</v>
       </c>
       <c r="D51" t="n">
-        <v>1271</v>
+        <v>1055</v>
       </c>
       <c r="E51" t="n">
-        <v>1172</v>
+        <v>995</v>
       </c>
       <c r="F51" t="n">
-        <v>1231</v>
+        <v>982</v>
       </c>
       <c r="G51" t="n">
-        <v>1075</v>
+        <v>1017</v>
       </c>
       <c r="H51" t="n">
-        <v>1100</v>
+        <v>984</v>
       </c>
       <c r="I51" t="n">
-        <v>1059</v>
+        <v>1019</v>
       </c>
       <c r="J51" t="n">
-        <v>1351</v>
+        <v>1088</v>
       </c>
       <c r="K51" t="n">
-        <v>1070</v>
+        <v>978</v>
       </c>
       <c r="L51" t="n">
-        <v>1184.1</v>
+        <v>1021.3</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1285.86</v>
+        <v>1110.22</v>
       </c>
       <c r="C52" t="n">
-        <v>1270.42</v>
+        <v>1115.34</v>
       </c>
       <c r="D52" t="n">
-        <v>1227.54</v>
+        <v>1107.14</v>
       </c>
       <c r="E52" t="n">
-        <v>1259.6</v>
+        <v>1089.3</v>
       </c>
       <c r="F52" t="n">
-        <v>1231.96</v>
+        <v>1111.24</v>
       </c>
       <c r="G52" t="n">
-        <v>1247.92</v>
+        <v>1092.62</v>
       </c>
       <c r="H52" t="n">
-        <v>1257.86</v>
+        <v>1128.52</v>
       </c>
       <c r="I52" t="n">
-        <v>1278.38</v>
+        <v>1132.58</v>
       </c>
       <c r="J52" t="n">
-        <v>1230.84</v>
+        <v>1105.02</v>
       </c>
       <c r="K52" t="n">
-        <v>1231.02</v>
+        <v>1107.8</v>
       </c>
       <c r="L52" t="n">
-        <v>1252.14</v>
+        <v>1109.978</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>16.64418530464172</v>
+        <v>13.13165831565857</v>
       </c>
       <c r="C2" t="n">
-        <v>18.04424285888672</v>
+        <v>12.69805955886841</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30279445648193</v>
+        <v>12.29589676856995</v>
       </c>
       <c r="E2" t="n">
-        <v>14.57066774368286</v>
+        <v>16.47161555290222</v>
       </c>
       <c r="F2" t="n">
-        <v>11.94101071357727</v>
+        <v>12.21871209144592</v>
       </c>
       <c r="G2" t="n">
-        <v>15.46404480934143</v>
+        <v>13.35137343406677</v>
       </c>
       <c r="H2" t="n">
-        <v>12.33629155158997</v>
+        <v>12.57780265808105</v>
       </c>
       <c r="I2" t="n">
-        <v>12.27167272567749</v>
+        <v>13.27975940704346</v>
       </c>
       <c r="J2" t="n">
-        <v>19.13101673126221</v>
+        <v>13.42267966270447</v>
       </c>
       <c r="K2" t="n">
-        <v>13.2457070350647</v>
+        <v>14.8766565322876</v>
       </c>
       <c r="L2" t="n">
-        <v>14.99516339302063</v>
+        <v>13.43242139816284</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>13.11334919929504</v>
+        <v>14.91918778419495</v>
       </c>
       <c r="C3" t="n">
-        <v>14.84833264350891</v>
+        <v>12.53800702095032</v>
       </c>
       <c r="D3" t="n">
-        <v>16.77056407928467</v>
+        <v>18.17025208473206</v>
       </c>
       <c r="E3" t="n">
-        <v>19.09271097183228</v>
+        <v>11.30551195144653</v>
       </c>
       <c r="F3" t="n">
-        <v>18.68742108345032</v>
+        <v>12.11842966079712</v>
       </c>
       <c r="G3" t="n">
-        <v>14.4884569644928</v>
+        <v>17.1144814491272</v>
       </c>
       <c r="H3" t="n">
-        <v>12.22376298904419</v>
+        <v>15.17572045326233</v>
       </c>
       <c r="I3" t="n">
-        <v>17.26190972328186</v>
+        <v>11.52608299255371</v>
       </c>
       <c r="J3" t="n">
-        <v>11.47383713722229</v>
+        <v>11.0112841129303</v>
       </c>
       <c r="K3" t="n">
-        <v>16.57248377799988</v>
+        <v>11.92833280563354</v>
       </c>
       <c r="L3" t="n">
-        <v>15.45328285694122</v>
+        <v>13.58072903156281</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>11.92549085617065</v>
+        <v>14.19145107269287</v>
       </c>
       <c r="C4" t="n">
-        <v>18.15834808349609</v>
+        <v>13.25112271308899</v>
       </c>
       <c r="D4" t="n">
-        <v>13.68217825889587</v>
+        <v>25.51521992683411</v>
       </c>
       <c r="E4" t="n">
-        <v>18.98679137229919</v>
+        <v>14.36506509780884</v>
       </c>
       <c r="F4" t="n">
-        <v>14.44524431228638</v>
+        <v>12.5225191116333</v>
       </c>
       <c r="G4" t="n">
-        <v>13.14796376228333</v>
+        <v>13.62028837203979</v>
       </c>
       <c r="H4" t="n">
-        <v>13.13179516792297</v>
+        <v>12.68539142608643</v>
       </c>
       <c r="I4" t="n">
-        <v>17.35137462615967</v>
+        <v>14.60217499732971</v>
       </c>
       <c r="J4" t="n">
-        <v>14.03133893013</v>
+        <v>17.14971017837524</v>
       </c>
       <c r="K4" t="n">
-        <v>17.64042997360229</v>
+        <v>12.24653029441833</v>
       </c>
       <c r="L4" t="n">
-        <v>15.25009553432465</v>
+        <v>15.01494731903076</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>11.92899131774902</v>
+        <v>10.27772092819214</v>
       </c>
       <c r="C5" t="n">
-        <v>13.44466829299927</v>
+        <v>10.57569670677185</v>
       </c>
       <c r="D5" t="n">
-        <v>13.54677367210388</v>
+        <v>12.22485995292664</v>
       </c>
       <c r="E5" t="n">
-        <v>12.64852070808411</v>
+        <v>11.33404111862183</v>
       </c>
       <c r="F5" t="n">
-        <v>11.27822256088257</v>
+        <v>10.27682662010193</v>
       </c>
       <c r="G5" t="n">
-        <v>11.94998812675476</v>
+        <v>11.38754153251648</v>
       </c>
       <c r="H5" t="n">
-        <v>15.48749709129333</v>
+        <v>10.50516223907471</v>
       </c>
       <c r="I5" t="n">
-        <v>17.28375339508057</v>
+        <v>11.91225218772888</v>
       </c>
       <c r="J5" t="n">
-        <v>11.72835254669189</v>
+        <v>10.31122970581055</v>
       </c>
       <c r="K5" t="n">
-        <v>12.53369450569153</v>
+        <v>11.16001725196838</v>
       </c>
       <c r="L5" t="n">
-        <v>13.18304622173309</v>
+        <v>10.99653482437134</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51226377487183</v>
+        <v>11.37660551071167</v>
       </c>
       <c r="C6" t="n">
-        <v>15.89701437950134</v>
+        <v>11.95340609550476</v>
       </c>
       <c r="D6" t="n">
-        <v>12.33692216873169</v>
+        <v>12.52687382698059</v>
       </c>
       <c r="E6" t="n">
-        <v>14.15758967399597</v>
+        <v>11.86951613426208</v>
       </c>
       <c r="F6" t="n">
-        <v>13.13548493385315</v>
+        <v>12.21747970581055</v>
       </c>
       <c r="G6" t="n">
-        <v>12.37629389762878</v>
+        <v>11.14156889915466</v>
       </c>
       <c r="H6" t="n">
-        <v>15.20458841323853</v>
+        <v>11.40482187271118</v>
       </c>
       <c r="I6" t="n">
-        <v>14.07668828964233</v>
+        <v>11.56319546699524</v>
       </c>
       <c r="J6" t="n">
-        <v>12.62312769889832</v>
+        <v>11.44728636741638</v>
       </c>
       <c r="K6" t="n">
-        <v>13.03605651855469</v>
+        <v>11.34915208816528</v>
       </c>
       <c r="L6" t="n">
-        <v>13.53560297489166</v>
+        <v>11.68499059677124</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>12.72484827041626</v>
+        <v>15.55890035629272</v>
       </c>
       <c r="C7" t="n">
-        <v>12.84229516983032</v>
+        <v>15.45598244667053</v>
       </c>
       <c r="D7" t="n">
-        <v>12.55203676223755</v>
+        <v>12.48557043075562</v>
       </c>
       <c r="E7" t="n">
-        <v>12.92415642738342</v>
+        <v>17.77859568595886</v>
       </c>
       <c r="F7" t="n">
-        <v>14.19626522064209</v>
+        <v>14.55079245567322</v>
       </c>
       <c r="G7" t="n">
-        <v>14.36315965652466</v>
+        <v>12.9333131313324</v>
       </c>
       <c r="H7" t="n">
-        <v>12.72238540649414</v>
+        <v>11.77673697471619</v>
       </c>
       <c r="I7" t="n">
-        <v>13.53941774368286</v>
+        <v>13.01301217079163</v>
       </c>
       <c r="J7" t="n">
-        <v>11.91763544082642</v>
+        <v>12.72197866439819</v>
       </c>
       <c r="K7" t="n">
-        <v>12.97602677345276</v>
+        <v>13.88885807991028</v>
       </c>
       <c r="L7" t="n">
-        <v>13.07582268714905</v>
+        <v>14.01637403964996</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>14.11630249023438</v>
+        <v>16.76233053207397</v>
       </c>
       <c r="C8" t="n">
-        <v>13.6677770614624</v>
+        <v>18.54352688789368</v>
       </c>
       <c r="D8" t="n">
-        <v>11.77435636520386</v>
+        <v>15.76278424263</v>
       </c>
       <c r="E8" t="n">
-        <v>12.30939936637878</v>
+        <v>12.73356533050537</v>
       </c>
       <c r="F8" t="n">
-        <v>12.14537882804871</v>
+        <v>12.43316435813904</v>
       </c>
       <c r="G8" t="n">
-        <v>12.34664463996887</v>
+        <v>11.09245252609253</v>
       </c>
       <c r="H8" t="n">
-        <v>12.76468586921692</v>
+        <v>12.50703263282776</v>
       </c>
       <c r="I8" t="n">
-        <v>11.37377595901489</v>
+        <v>12.77782368659973</v>
       </c>
       <c r="J8" t="n">
-        <v>12.03230738639832</v>
+        <v>11.71821188926697</v>
       </c>
       <c r="K8" t="n">
-        <v>12.12798500061035</v>
+        <v>12.15813779830933</v>
       </c>
       <c r="L8" t="n">
-        <v>12.46586129665375</v>
+        <v>13.64890298843384</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8984534740448</v>
+        <v>11.83642530441284</v>
       </c>
       <c r="C9" t="n">
-        <v>17.04229545593262</v>
+        <v>12.29809641838074</v>
       </c>
       <c r="D9" t="n">
-        <v>12.14647388458252</v>
+        <v>12.29976034164429</v>
       </c>
       <c r="E9" t="n">
-        <v>11.75044846534729</v>
+        <v>11.71293044090271</v>
       </c>
       <c r="F9" t="n">
-        <v>12.55187845230103</v>
+        <v>13.44000792503357</v>
       </c>
       <c r="G9" t="n">
-        <v>11.16397976875305</v>
+        <v>12.03446340560913</v>
       </c>
       <c r="H9" t="n">
-        <v>14.13548994064331</v>
+        <v>13.67462873458862</v>
       </c>
       <c r="I9" t="n">
-        <v>12.53296637535095</v>
+        <v>13.97562599182129</v>
       </c>
       <c r="J9" t="n">
-        <v>13.0699303150177</v>
+        <v>12.36393666267395</v>
       </c>
       <c r="K9" t="n">
-        <v>15.47452092170715</v>
+        <v>12.04478979110718</v>
       </c>
       <c r="L9" t="n">
-        <v>13.47664370536804</v>
+        <v>12.56806650161743</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>12.48956036567688</v>
+        <v>14.72235131263733</v>
       </c>
       <c r="C10" t="n">
-        <v>18.12898302078247</v>
+        <v>12.5893337726593</v>
       </c>
       <c r="D10" t="n">
-        <v>13.36395978927612</v>
+        <v>11.85330677032471</v>
       </c>
       <c r="E10" t="n">
-        <v>13.16278052330017</v>
+        <v>13.53380799293518</v>
       </c>
       <c r="F10" t="n">
-        <v>11.80894231796265</v>
+        <v>12.08049249649048</v>
       </c>
       <c r="G10" t="n">
-        <v>16.00114297866821</v>
+        <v>12.51300406455994</v>
       </c>
       <c r="H10" t="n">
-        <v>12.41000461578369</v>
+        <v>12.95157670974731</v>
       </c>
       <c r="I10" t="n">
-        <v>13.68448925018311</v>
+        <v>12.52141308784485</v>
       </c>
       <c r="J10" t="n">
-        <v>13.98057198524475</v>
+        <v>12.90612769126892</v>
       </c>
       <c r="K10" t="n">
-        <v>14.49720978736877</v>
+        <v>13.34132266044617</v>
       </c>
       <c r="L10" t="n">
-        <v>13.95276446342468</v>
+        <v>12.90127365589142</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>15.75892448425293</v>
+        <v>13.03089475631714</v>
       </c>
       <c r="C11" t="n">
-        <v>13.44520998001099</v>
+        <v>13.28746652603149</v>
       </c>
       <c r="D11" t="n">
-        <v>16.28929352760315</v>
+        <v>13.1069495677948</v>
       </c>
       <c r="E11" t="n">
-        <v>11.87541580200195</v>
+        <v>12.76486349105835</v>
       </c>
       <c r="F11" t="n">
-        <v>15.74998092651367</v>
+        <v>18.32399797439575</v>
       </c>
       <c r="G11" t="n">
-        <v>13.30229020118713</v>
+        <v>14.28081011772156</v>
       </c>
       <c r="H11" t="n">
-        <v>13.82568311691284</v>
+        <v>14.44935941696167</v>
       </c>
       <c r="I11" t="n">
-        <v>13.82794976234436</v>
+        <v>14.59297490119934</v>
       </c>
       <c r="J11" t="n">
-        <v>12.09964728355408</v>
+        <v>14.70152592658997</v>
       </c>
       <c r="K11" t="n">
-        <v>12.70267844200134</v>
+        <v>17.51088666915894</v>
       </c>
       <c r="L11" t="n">
-        <v>13.88770735263824</v>
+        <v>14.6049729347229</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>19.37161803245544</v>
+        <v>14.20891189575195</v>
       </c>
       <c r="C12" t="n">
-        <v>14.34801506996155</v>
+        <v>14.36192965507507</v>
       </c>
       <c r="D12" t="n">
-        <v>13.40851950645447</v>
+        <v>13.52163934707642</v>
       </c>
       <c r="E12" t="n">
-        <v>12.74097394943237</v>
+        <v>14.278240442276</v>
       </c>
       <c r="F12" t="n">
-        <v>18.12749052047729</v>
+        <v>20.57178449630737</v>
       </c>
       <c r="G12" t="n">
-        <v>18.50855350494385</v>
+        <v>14.38897466659546</v>
       </c>
       <c r="H12" t="n">
-        <v>17.12628865242004</v>
+        <v>14.29123401641846</v>
       </c>
       <c r="I12" t="n">
-        <v>14.93215537071228</v>
+        <v>14.16462469100952</v>
       </c>
       <c r="J12" t="n">
-        <v>13.62669253349304</v>
+        <v>18.43418049812317</v>
       </c>
       <c r="K12" t="n">
-        <v>15.0019862651825</v>
+        <v>15.87876868247986</v>
       </c>
       <c r="L12" t="n">
-        <v>15.71922934055328</v>
+        <v>15.41002883911133</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>13.7403621673584</v>
+        <v>18.14864349365234</v>
       </c>
       <c r="C13" t="n">
-        <v>14.96254444122314</v>
+        <v>14.35508871078491</v>
       </c>
       <c r="D13" t="n">
-        <v>13.32564759254456</v>
+        <v>18.42358636856079</v>
       </c>
       <c r="E13" t="n">
-        <v>13.92716479301453</v>
+        <v>13.59553194046021</v>
       </c>
       <c r="F13" t="n">
-        <v>14.69683337211609</v>
+        <v>13.5897479057312</v>
       </c>
       <c r="G13" t="n">
-        <v>17.65346169471741</v>
+        <v>15.64246082305908</v>
       </c>
       <c r="H13" t="n">
-        <v>14.49198007583618</v>
+        <v>14.88613343238831</v>
       </c>
       <c r="I13" t="n">
-        <v>13.09302139282227</v>
+        <v>15.34390425682068</v>
       </c>
       <c r="J13" t="n">
-        <v>15.37451982498169</v>
+        <v>14.14348363876343</v>
       </c>
       <c r="K13" t="n">
-        <v>14.32695412635803</v>
+        <v>13.43776726722717</v>
       </c>
       <c r="L13" t="n">
-        <v>14.55924894809723</v>
+        <v>15.15663478374481</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>17.78571653366089</v>
+        <v>12.93805480003357</v>
       </c>
       <c r="C14" t="n">
-        <v>12.77127838134766</v>
+        <v>13.02182483673096</v>
       </c>
       <c r="D14" t="n">
-        <v>12.45817589759827</v>
+        <v>13.19666147232056</v>
       </c>
       <c r="E14" t="n">
-        <v>13.97734570503235</v>
+        <v>13.359379529953</v>
       </c>
       <c r="F14" t="n">
-        <v>14.19998240470886</v>
+        <v>13.1934232711792</v>
       </c>
       <c r="G14" t="n">
-        <v>15.56146764755249</v>
+        <v>14.37246584892273</v>
       </c>
       <c r="H14" t="n">
-        <v>14.78996300697327</v>
+        <v>16.03260183334351</v>
       </c>
       <c r="I14" t="n">
-        <v>12.52653193473816</v>
+        <v>14.65349340438843</v>
       </c>
       <c r="J14" t="n">
-        <v>19.38379311561584</v>
+        <v>13.67236256599426</v>
       </c>
       <c r="K14" t="n">
-        <v>13.95015978813171</v>
+        <v>13.47196197509766</v>
       </c>
       <c r="L14" t="n">
-        <v>14.74044144153595</v>
+        <v>13.79122295379639</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16.5639009475708</v>
+        <v>13.93820190429688</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82521939277649</v>
+        <v>13.20774364471436</v>
       </c>
       <c r="D15" t="n">
-        <v>17.65065455436707</v>
+        <v>12.63429379463196</v>
       </c>
       <c r="E15" t="n">
-        <v>14.55222535133362</v>
+        <v>12.79430103302002</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49695324897766</v>
+        <v>12.67688846588135</v>
       </c>
       <c r="G15" t="n">
-        <v>15.84582281112671</v>
+        <v>13.32714438438416</v>
       </c>
       <c r="H15" t="n">
-        <v>19.51880073547363</v>
+        <v>12.41978716850281</v>
       </c>
       <c r="I15" t="n">
-        <v>12.59609699249268</v>
+        <v>13.1673595905304</v>
       </c>
       <c r="J15" t="n">
-        <v>11.61771106719971</v>
+        <v>12.68268322944641</v>
       </c>
       <c r="K15" t="n">
-        <v>13.16689133644104</v>
+        <v>13.61022233963013</v>
       </c>
       <c r="L15" t="n">
-        <v>14.58342764377594</v>
+        <v>13.04586255550385</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>12.78409504890442</v>
+        <v>13.63781595230103</v>
       </c>
       <c r="C16" t="n">
-        <v>17.33916687965393</v>
+        <v>13.17959594726562</v>
       </c>
       <c r="D16" t="n">
-        <v>13.45991802215576</v>
+        <v>13.22843933105469</v>
       </c>
       <c r="E16" t="n">
-        <v>13.25480031967163</v>
+        <v>13.60807275772095</v>
       </c>
       <c r="F16" t="n">
-        <v>13.93400692939758</v>
+        <v>13.38834547996521</v>
       </c>
       <c r="G16" t="n">
-        <v>12.71600365638733</v>
+        <v>13.16659617424011</v>
       </c>
       <c r="H16" t="n">
-        <v>12.81249499320984</v>
+        <v>14.0979950428009</v>
       </c>
       <c r="I16" t="n">
-        <v>13.17126870155334</v>
+        <v>16.24676537513733</v>
       </c>
       <c r="J16" t="n">
-        <v>11.72124218940735</v>
+        <v>13.06236124038696</v>
       </c>
       <c r="K16" t="n">
-        <v>12.92048120498657</v>
+        <v>16.14628005027771</v>
       </c>
       <c r="L16" t="n">
-        <v>13.41134779453278</v>
+        <v>13.97622673511505</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>12.24307918548584</v>
+        <v>13.24268174171448</v>
       </c>
       <c r="C17" t="n">
-        <v>14.57494139671326</v>
+        <v>11.50482487678528</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15108776092529</v>
+        <v>11.94123029708862</v>
       </c>
       <c r="E17" t="n">
-        <v>15.30237221717834</v>
+        <v>14.34708499908447</v>
       </c>
       <c r="F17" t="n">
-        <v>16.80487179756165</v>
+        <v>12.58886075019836</v>
       </c>
       <c r="G17" t="n">
-        <v>12.97221064567566</v>
+        <v>12.43829035758972</v>
       </c>
       <c r="H17" t="n">
-        <v>16.69786763191223</v>
+        <v>13.76161646842957</v>
       </c>
       <c r="I17" t="n">
-        <v>13.08815455436707</v>
+        <v>11.17674446105957</v>
       </c>
       <c r="J17" t="n">
-        <v>15.63049221038818</v>
+        <v>11.67432475090027</v>
       </c>
       <c r="K17" t="n">
-        <v>16.25902390480042</v>
+        <v>13.02726078033447</v>
       </c>
       <c r="L17" t="n">
-        <v>14.67241013050079</v>
+        <v>12.57029194831848</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>16.70061469078064</v>
+        <v>13.00642347335815</v>
       </c>
       <c r="C18" t="n">
-        <v>19.15419960021973</v>
+        <v>13.94930338859558</v>
       </c>
       <c r="D18" t="n">
-        <v>12.17166996002197</v>
+        <v>11.89171075820923</v>
       </c>
       <c r="E18" t="n">
-        <v>18.33401131629944</v>
+        <v>13.93427872657776</v>
       </c>
       <c r="F18" t="n">
-        <v>12.3274941444397</v>
+        <v>12.05364537239075</v>
       </c>
       <c r="G18" t="n">
-        <v>15.80588364601135</v>
+        <v>14.27270293235779</v>
       </c>
       <c r="H18" t="n">
-        <v>12.64515376091003</v>
+        <v>12.61749243736267</v>
       </c>
       <c r="I18" t="n">
-        <v>17.98533368110657</v>
+        <v>12.53278183937073</v>
       </c>
       <c r="J18" t="n">
-        <v>12.01662945747375</v>
+        <v>15.99845266342163</v>
       </c>
       <c r="K18" t="n">
-        <v>13.14113664627075</v>
+        <v>12.70338821411133</v>
       </c>
       <c r="L18" t="n">
-        <v>15.02821269035339</v>
+        <v>13.29601798057556</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>13.21050119400024</v>
+        <v>14.24962186813354</v>
       </c>
       <c r="C19" t="n">
-        <v>13.37954449653625</v>
+        <v>14.12400603294373</v>
       </c>
       <c r="D19" t="n">
-        <v>13.21343851089478</v>
+        <v>13.99743556976318</v>
       </c>
       <c r="E19" t="n">
-        <v>19.04608511924744</v>
+        <v>14.284348487854</v>
       </c>
       <c r="F19" t="n">
-        <v>12.70112061500549</v>
+        <v>16.05467653274536</v>
       </c>
       <c r="G19" t="n">
-        <v>12.31757020950317</v>
+        <v>12.16700863838196</v>
       </c>
       <c r="H19" t="n">
-        <v>16.61240386962891</v>
+        <v>14.19770884513855</v>
       </c>
       <c r="I19" t="n">
-        <v>12.29576730728149</v>
+        <v>14.82656097412109</v>
       </c>
       <c r="J19" t="n">
-        <v>14.84907507896423</v>
+        <v>12.30414247512817</v>
       </c>
       <c r="K19" t="n">
-        <v>12.54687809944153</v>
+        <v>13.47276306152344</v>
       </c>
       <c r="L19" t="n">
-        <v>14.01723845005035</v>
+        <v>13.9678272485733</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>17.65150809288025</v>
+        <v>15.99441528320312</v>
       </c>
       <c r="C20" t="n">
-        <v>11.6073591709137</v>
+        <v>16.48486161231995</v>
       </c>
       <c r="D20" t="n">
-        <v>12.64283657073975</v>
+        <v>12.14238405227661</v>
       </c>
       <c r="E20" t="n">
-        <v>14.79336905479431</v>
+        <v>16.72814464569092</v>
       </c>
       <c r="F20" t="n">
-        <v>18.30309748649597</v>
+        <v>12.48186254501343</v>
       </c>
       <c r="G20" t="n">
-        <v>12.02099275588989</v>
+        <v>10.91179347038269</v>
       </c>
       <c r="H20" t="n">
-        <v>12.211834192276</v>
+        <v>15.712486743927</v>
       </c>
       <c r="I20" t="n">
-        <v>16.19009280204773</v>
+        <v>12.94864821434021</v>
       </c>
       <c r="J20" t="n">
-        <v>12.64894342422485</v>
+        <v>14.81343650817871</v>
       </c>
       <c r="K20" t="n">
-        <v>13.23919939994812</v>
+        <v>12.22076439857483</v>
       </c>
       <c r="L20" t="n">
-        <v>14.13092329502106</v>
+        <v>14.04387974739075</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>17.95948100090027</v>
+        <v>11.88602757453918</v>
       </c>
       <c r="C21" t="n">
-        <v>15.23849773406982</v>
+        <v>13.42702507972717</v>
       </c>
       <c r="D21" t="n">
-        <v>14.06001782417297</v>
+        <v>14.13002753257751</v>
       </c>
       <c r="E21" t="n">
-        <v>12.97028636932373</v>
+        <v>11.53481364250183</v>
       </c>
       <c r="F21" t="n">
-        <v>17.37159657478333</v>
+        <v>12.15566372871399</v>
       </c>
       <c r="G21" t="n">
-        <v>11.74094486236572</v>
+        <v>11.75432276725769</v>
       </c>
       <c r="H21" t="n">
-        <v>15.48801136016846</v>
+        <v>11.51854538917542</v>
       </c>
       <c r="I21" t="n">
-        <v>17.10969042778015</v>
+        <v>13.09657955169678</v>
       </c>
       <c r="J21" t="n">
-        <v>17.72944307327271</v>
+        <v>11.77874112129211</v>
       </c>
       <c r="K21" t="n">
-        <v>12.92726039886475</v>
+        <v>11.87386131286621</v>
       </c>
       <c r="L21" t="n">
-        <v>15.25952296257019</v>
+        <v>12.31556077003479</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>13.38904500007629</v>
+        <v>11.12220931053162</v>
       </c>
       <c r="C22" t="n">
-        <v>12.04628872871399</v>
+        <v>12.62646675109863</v>
       </c>
       <c r="D22" t="n">
-        <v>12.47695064544678</v>
+        <v>12.33251762390137</v>
       </c>
       <c r="E22" t="n">
-        <v>14.69050407409668</v>
+        <v>12.60306477546692</v>
       </c>
       <c r="F22" t="n">
-        <v>12.31869435310364</v>
+        <v>15.72323369979858</v>
       </c>
       <c r="G22" t="n">
-        <v>12.07734298706055</v>
+        <v>12.17721128463745</v>
       </c>
       <c r="H22" t="n">
-        <v>14.27479481697083</v>
+        <v>12.8387725353241</v>
       </c>
       <c r="I22" t="n">
-        <v>12.8742401599884</v>
+        <v>13.95268607139587</v>
       </c>
       <c r="J22" t="n">
-        <v>13.23326539993286</v>
+        <v>11.50097870826721</v>
       </c>
       <c r="K22" t="n">
-        <v>15.79906177520752</v>
+        <v>12.91082072257996</v>
       </c>
       <c r="L22" t="n">
-        <v>13.31801879405975</v>
+        <v>12.77879614830017</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>11.51166820526123</v>
+        <v>11.69885468482971</v>
       </c>
       <c r="C23" t="n">
-        <v>15.62399983406067</v>
+        <v>11.06767439842224</v>
       </c>
       <c r="D23" t="n">
-        <v>12.11070489883423</v>
+        <v>11.20584535598755</v>
       </c>
       <c r="E23" t="n">
-        <v>11.38321089744568</v>
+        <v>11.29890584945679</v>
       </c>
       <c r="F23" t="n">
-        <v>12.21034121513367</v>
+        <v>12.80029964447021</v>
       </c>
       <c r="G23" t="n">
-        <v>16.7136013507843</v>
+        <v>11.20384955406189</v>
       </c>
       <c r="H23" t="n">
-        <v>15.91598105430603</v>
+        <v>11.33493065834045</v>
       </c>
       <c r="I23" t="n">
-        <v>16.56610012054443</v>
+        <v>10.61415100097656</v>
       </c>
       <c r="J23" t="n">
-        <v>15.5418872833252</v>
+        <v>11.48372936248779</v>
       </c>
       <c r="K23" t="n">
-        <v>11.99158191680908</v>
+        <v>11.55421304702759</v>
       </c>
       <c r="L23" t="n">
-        <v>13.95690767765045</v>
+        <v>11.42624535560608</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>13.72070169448853</v>
+        <v>13.14525437355042</v>
       </c>
       <c r="C24" t="n">
-        <v>14.55162000656128</v>
+        <v>19.88423418998718</v>
       </c>
       <c r="D24" t="n">
-        <v>17.86110162734985</v>
+        <v>13.92182421684265</v>
       </c>
       <c r="E24" t="n">
-        <v>13.20282626152039</v>
+        <v>13.22516822814941</v>
       </c>
       <c r="F24" t="n">
-        <v>14.16124105453491</v>
+        <v>12.98801064491272</v>
       </c>
       <c r="G24" t="n">
-        <v>15.57673978805542</v>
+        <v>13.98917627334595</v>
       </c>
       <c r="H24" t="n">
-        <v>15.35604882240295</v>
+        <v>13.28346800804138</v>
       </c>
       <c r="I24" t="n">
-        <v>16.48766255378723</v>
+        <v>13.79593801498413</v>
       </c>
       <c r="J24" t="n">
-        <v>15.71524047851562</v>
+        <v>14.07496070861816</v>
       </c>
       <c r="K24" t="n">
-        <v>12.95384192466736</v>
+        <v>14.81880283355713</v>
       </c>
       <c r="L24" t="n">
-        <v>14.95870242118835</v>
+        <v>14.31268374919891</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>14.0056586265564</v>
+        <v>18.95298552513123</v>
       </c>
       <c r="C25" t="n">
-        <v>14.39914417266846</v>
+        <v>16.0675835609436</v>
       </c>
       <c r="D25" t="n">
-        <v>13.46969199180603</v>
+        <v>16.41011548042297</v>
       </c>
       <c r="E25" t="n">
-        <v>14.64963412284851</v>
+        <v>18.64332914352417</v>
       </c>
       <c r="F25" t="n">
-        <v>19.18644952774048</v>
+        <v>15.73805117607117</v>
       </c>
       <c r="G25" t="n">
-        <v>18.32030367851257</v>
+        <v>14.28660464286804</v>
       </c>
       <c r="H25" t="n">
-        <v>14.53007888793945</v>
+        <v>20.071457862854</v>
       </c>
       <c r="I25" t="n">
-        <v>14.43996334075928</v>
+        <v>16.23996257781982</v>
       </c>
       <c r="J25" t="n">
-        <v>14.22915744781494</v>
+        <v>18.19372987747192</v>
       </c>
       <c r="K25" t="n">
-        <v>14.02129197120667</v>
+        <v>19.41301846504211</v>
       </c>
       <c r="L25" t="n">
-        <v>15.12513737678528</v>
+        <v>17.4016838312149</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>11.76974844932556</v>
+        <v>14.72468161582947</v>
       </c>
       <c r="C26" t="n">
-        <v>14.82159543037415</v>
+        <v>14.79338479042053</v>
       </c>
       <c r="D26" t="n">
-        <v>11.57607007026672</v>
+        <v>12.17451739311218</v>
       </c>
       <c r="E26" t="n">
-        <v>15.30445218086243</v>
+        <v>13.3163890838623</v>
       </c>
       <c r="F26" t="n">
-        <v>13.11615967750549</v>
+        <v>12.2392692565918</v>
       </c>
       <c r="G26" t="n">
-        <v>11.38385343551636</v>
+        <v>11.59100365638733</v>
       </c>
       <c r="H26" t="n">
-        <v>28.2021803855896</v>
+        <v>11.90416574478149</v>
       </c>
       <c r="I26" t="n">
-        <v>14.86121153831482</v>
+        <v>11.42544555664062</v>
       </c>
       <c r="J26" t="n">
-        <v>13.2935106754303</v>
+        <v>11.40150952339172</v>
       </c>
       <c r="K26" t="n">
-        <v>11.65745139122009</v>
+        <v>11.38555240631104</v>
       </c>
       <c r="L26" t="n">
-        <v>14.59862332344055</v>
+        <v>12.49559190273285</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>13.61099100112915</v>
+        <v>13.59464573860168</v>
       </c>
       <c r="C27" t="n">
-        <v>14.25962257385254</v>
+        <v>17.32766151428223</v>
       </c>
       <c r="D27" t="n">
-        <v>16.21073794364929</v>
+        <v>12.80376029014587</v>
       </c>
       <c r="E27" t="n">
-        <v>12.56387972831726</v>
+        <v>12.49957394599915</v>
       </c>
       <c r="F27" t="n">
-        <v>12.27932262420654</v>
+        <v>13.8579409122467</v>
       </c>
       <c r="G27" t="n">
-        <v>13.93743014335632</v>
+        <v>11.77750515937805</v>
       </c>
       <c r="H27" t="n">
-        <v>13.10600996017456</v>
+        <v>15.12654852867126</v>
       </c>
       <c r="I27" t="n">
-        <v>12.73253917694092</v>
+        <v>17.42041397094727</v>
       </c>
       <c r="J27" t="n">
-        <v>13.05829644203186</v>
+        <v>13.649498462677</v>
       </c>
       <c r="K27" t="n">
-        <v>14.0651478767395</v>
+        <v>12.64618182182312</v>
       </c>
       <c r="L27" t="n">
-        <v>13.5823977470398</v>
+        <v>14.07037303447723</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>14.28069663047791</v>
+        <v>15.30124640464783</v>
       </c>
       <c r="C28" t="n">
-        <v>12.54558944702148</v>
+        <v>12.76885318756104</v>
       </c>
       <c r="D28" t="n">
-        <v>13.01132678985596</v>
+        <v>12.74817061424255</v>
       </c>
       <c r="E28" t="n">
-        <v>11.73989009857178</v>
+        <v>12.40881729125977</v>
       </c>
       <c r="F28" t="n">
-        <v>13.31009960174561</v>
+        <v>17.78785419464111</v>
       </c>
       <c r="G28" t="n">
-        <v>16.02453398704529</v>
+        <v>12.91222786903381</v>
       </c>
       <c r="H28" t="n">
-        <v>12.85139083862305</v>
+        <v>16.70931601524353</v>
       </c>
       <c r="I28" t="n">
-        <v>11.67545032501221</v>
+        <v>13.70282959938049</v>
       </c>
       <c r="J28" t="n">
-        <v>12.24265933036804</v>
+        <v>13.60569643974304</v>
       </c>
       <c r="K28" t="n">
-        <v>13.15619826316833</v>
+        <v>12.83574390411377</v>
       </c>
       <c r="L28" t="n">
-        <v>13.08378353118897</v>
+        <v>14.07807555198669</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>12.84074258804321</v>
+        <v>11.31972813606262</v>
       </c>
       <c r="C29" t="n">
-        <v>16.68819189071655</v>
+        <v>11.87823534011841</v>
       </c>
       <c r="D29" t="n">
-        <v>12.03292226791382</v>
+        <v>13.81904458999634</v>
       </c>
       <c r="E29" t="n">
-        <v>12.41242218017578</v>
+        <v>11.77152013778687</v>
       </c>
       <c r="F29" t="n">
-        <v>11.40671014785767</v>
+        <v>11.1810998916626</v>
       </c>
       <c r="G29" t="n">
-        <v>11.65207695960999</v>
+        <v>11.22797393798828</v>
       </c>
       <c r="H29" t="n">
-        <v>12.44543814659119</v>
+        <v>10.54978799819946</v>
       </c>
       <c r="I29" t="n">
-        <v>15.54784536361694</v>
+        <v>11.3791036605835</v>
       </c>
       <c r="J29" t="n">
-        <v>18.01574182510376</v>
+        <v>11.84632039070129</v>
       </c>
       <c r="K29" t="n">
-        <v>10.80704426765442</v>
+        <v>11.39253377914429</v>
       </c>
       <c r="L29" t="n">
-        <v>13.38491356372833</v>
+        <v>11.63653478622436</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>18.1887321472168</v>
+        <v>12.53747224807739</v>
       </c>
       <c r="C30" t="n">
-        <v>17.16752815246582</v>
+        <v>11.70170712471008</v>
       </c>
       <c r="D30" t="n">
-        <v>12.94292545318604</v>
+        <v>15.03579139709473</v>
       </c>
       <c r="E30" t="n">
-        <v>15.10693264007568</v>
+        <v>12.42178153991699</v>
       </c>
       <c r="F30" t="n">
-        <v>15.34962034225464</v>
+        <v>13.16800045967102</v>
       </c>
       <c r="G30" t="n">
-        <v>17.47139000892639</v>
+        <v>12.36593103408813</v>
       </c>
       <c r="H30" t="n">
-        <v>15.04337668418884</v>
+        <v>12.83866691589355</v>
       </c>
       <c r="I30" t="n">
-        <v>12.95391130447388</v>
+        <v>15.29911518096924</v>
       </c>
       <c r="J30" t="n">
-        <v>15.13916778564453</v>
+        <v>13.41502547264099</v>
       </c>
       <c r="K30" t="n">
-        <v>12.95762848854065</v>
+        <v>15.88580584526062</v>
       </c>
       <c r="L30" t="n">
-        <v>15.23212130069733</v>
+        <v>13.46692972183228</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>16.19863653182983</v>
+        <v>14.76052713394165</v>
       </c>
       <c r="C31" t="n">
-        <v>11.91410422325134</v>
+        <v>14.97772264480591</v>
       </c>
       <c r="D31" t="n">
-        <v>19.58119058609009</v>
+        <v>13.50372242927551</v>
       </c>
       <c r="E31" t="n">
-        <v>16.08251452445984</v>
+        <v>13.01946115493774</v>
       </c>
       <c r="F31" t="n">
-        <v>15.45560503005981</v>
+        <v>12.18412804603577</v>
       </c>
       <c r="G31" t="n">
-        <v>16.2705512046814</v>
+        <v>14.03355145454407</v>
       </c>
       <c r="H31" t="n">
-        <v>17.83918428421021</v>
+        <v>12.2331657409668</v>
       </c>
       <c r="I31" t="n">
-        <v>13.02531552314758</v>
+        <v>16.49230766296387</v>
       </c>
       <c r="J31" t="n">
-        <v>12.90142416954041</v>
+        <v>16.34945797920227</v>
       </c>
       <c r="K31" t="n">
-        <v>12.25592041015625</v>
+        <v>13.1633985042572</v>
       </c>
       <c r="L31" t="n">
-        <v>15.15244464874268</v>
+        <v>14.07174427509308</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>15.50536131858826</v>
+        <v>15.24654579162598</v>
       </c>
       <c r="C32" t="n">
-        <v>12.80573582649231</v>
+        <v>13.67936682701111</v>
       </c>
       <c r="D32" t="n">
-        <v>16.00931644439697</v>
+        <v>11.62289905548096</v>
       </c>
       <c r="E32" t="n">
-        <v>15.8095543384552</v>
+        <v>10.86535334587097</v>
       </c>
       <c r="F32" t="n">
-        <v>12.1444878578186</v>
+        <v>11.36700320243835</v>
       </c>
       <c r="G32" t="n">
-        <v>11.64891719818115</v>
+        <v>11.23317432403564</v>
       </c>
       <c r="H32" t="n">
-        <v>14.60578107833862</v>
+        <v>12.41306495666504</v>
       </c>
       <c r="I32" t="n">
-        <v>11.90071535110474</v>
+        <v>17.61452436447144</v>
       </c>
       <c r="J32" t="n">
-        <v>12.20942449569702</v>
+        <v>10.22173023223877</v>
       </c>
       <c r="K32" t="n">
-        <v>12.061110496521</v>
+        <v>12.40661787986755</v>
       </c>
       <c r="L32" t="n">
-        <v>13.47004044055939</v>
+        <v>12.66702799797058</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>17.53525185585022</v>
+        <v>11.58945083618164</v>
       </c>
       <c r="C33" t="n">
-        <v>16.89132118225098</v>
+        <v>13.79840898513794</v>
       </c>
       <c r="D33" t="n">
-        <v>12.18678712844849</v>
+        <v>12.25984382629395</v>
       </c>
       <c r="E33" t="n">
-        <v>13.87449026107788</v>
+        <v>11.56182217597961</v>
       </c>
       <c r="F33" t="n">
-        <v>12.78715038299561</v>
+        <v>11.74399280548096</v>
       </c>
       <c r="G33" t="n">
-        <v>15.76113796234131</v>
+        <v>15.22016906738281</v>
       </c>
       <c r="H33" t="n">
-        <v>13.24179553985596</v>
+        <v>12.47697806358337</v>
       </c>
       <c r="I33" t="n">
-        <v>16.93094038963318</v>
+        <v>18.69790363311768</v>
       </c>
       <c r="J33" t="n">
-        <v>13.28822016716003</v>
+        <v>13.05611848831177</v>
       </c>
       <c r="K33" t="n">
-        <v>13.63629364967346</v>
+        <v>14.5306613445282</v>
       </c>
       <c r="L33" t="n">
-        <v>14.61333885192871</v>
+        <v>13.49353492259979</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>11.53229331970215</v>
+        <v>10.69899201393127</v>
       </c>
       <c r="C34" t="n">
-        <v>11.08039617538452</v>
+        <v>13.52264714241028</v>
       </c>
       <c r="D34" t="n">
-        <v>12.05183529853821</v>
+        <v>12.65773725509644</v>
       </c>
       <c r="E34" t="n">
-        <v>13.16586780548096</v>
+        <v>11.90252804756165</v>
       </c>
       <c r="F34" t="n">
-        <v>16.46243262290955</v>
+        <v>11.3972065448761</v>
       </c>
       <c r="G34" t="n">
-        <v>12.1304132938385</v>
+        <v>11.25908088684082</v>
       </c>
       <c r="H34" t="n">
-        <v>15.59001493453979</v>
+        <v>11.71340346336365</v>
       </c>
       <c r="I34" t="n">
-        <v>15.34474873542786</v>
+        <v>11.55326557159424</v>
       </c>
       <c r="J34" t="n">
-        <v>11.41801953315735</v>
+        <v>11.08303999900818</v>
       </c>
       <c r="K34" t="n">
-        <v>12.36684250831604</v>
+        <v>11.86356592178345</v>
       </c>
       <c r="L34" t="n">
-        <v>13.11428642272949</v>
+        <v>11.76514668464661</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>16.63595581054688</v>
+        <v>11.82557439804077</v>
       </c>
       <c r="C35" t="n">
-        <v>16.13266038894653</v>
+        <v>14.60868334770203</v>
       </c>
       <c r="D35" t="n">
-        <v>12.77836036682129</v>
+        <v>12.05239820480347</v>
       </c>
       <c r="E35" t="n">
-        <v>13.04540777206421</v>
+        <v>11.7969958782196</v>
       </c>
       <c r="F35" t="n">
-        <v>15.68545031547546</v>
+        <v>11.74926424026489</v>
       </c>
       <c r="G35" t="n">
-        <v>16.79315304756165</v>
+        <v>12.1571102142334</v>
       </c>
       <c r="H35" t="n">
-        <v>13.26518583297729</v>
+        <v>11.68239498138428</v>
       </c>
       <c r="I35" t="n">
-        <v>13.74313020706177</v>
+        <v>16.01420068740845</v>
       </c>
       <c r="J35" t="n">
-        <v>14.39353775978088</v>
+        <v>11.3410918712616</v>
       </c>
       <c r="K35" t="n">
-        <v>17.7580738067627</v>
+        <v>11.50736618041992</v>
       </c>
       <c r="L35" t="n">
-        <v>15.02309153079987</v>
+        <v>12.47350800037384</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>13.24489188194275</v>
+        <v>12.14790296554565</v>
       </c>
       <c r="C36" t="n">
-        <v>13.70052886009216</v>
+        <v>12.12269306182861</v>
       </c>
       <c r="D36" t="n">
-        <v>14.36135578155518</v>
+        <v>12.69533610343933</v>
       </c>
       <c r="E36" t="n">
-        <v>13.97046661376953</v>
+        <v>11.91010785102844</v>
       </c>
       <c r="F36" t="n">
-        <v>11.85205626487732</v>
+        <v>12.44314789772034</v>
       </c>
       <c r="G36" t="n">
-        <v>12.39309048652649</v>
+        <v>10.40665578842163</v>
       </c>
       <c r="H36" t="n">
-        <v>12.93656754493713</v>
+        <v>11.97072196006775</v>
       </c>
       <c r="I36" t="n">
-        <v>14.79691290855408</v>
+        <v>11.60660576820374</v>
       </c>
       <c r="J36" t="n">
-        <v>13.16446757316589</v>
+        <v>10.87900590896606</v>
       </c>
       <c r="K36" t="n">
-        <v>15.79869318008423</v>
+        <v>11.04679751396179</v>
       </c>
       <c r="L36" t="n">
-        <v>13.62190310955048</v>
+        <v>11.72289748191833</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>13.55884861946106</v>
+        <v>10.76887226104736</v>
       </c>
       <c r="C37" t="n">
-        <v>12.95580005645752</v>
+        <v>10.31482648849487</v>
       </c>
       <c r="D37" t="n">
-        <v>14.1117377281189</v>
+        <v>13.22146224975586</v>
       </c>
       <c r="E37" t="n">
-        <v>12.11198401451111</v>
+        <v>11.26425504684448</v>
       </c>
       <c r="F37" t="n">
-        <v>15.65416407585144</v>
+        <v>11.92491865158081</v>
       </c>
       <c r="G37" t="n">
-        <v>11.31104254722595</v>
+        <v>16.47522497177124</v>
       </c>
       <c r="H37" t="n">
-        <v>14.07520318031311</v>
+        <v>16.16027426719666</v>
       </c>
       <c r="I37" t="n">
-        <v>12.77132534980774</v>
+        <v>11.72579836845398</v>
       </c>
       <c r="J37" t="n">
-        <v>12.98588109016418</v>
+        <v>11.74034333229065</v>
       </c>
       <c r="K37" t="n">
-        <v>11.86507678031921</v>
+        <v>13.99996471405029</v>
       </c>
       <c r="L37" t="n">
-        <v>13.14010634422302</v>
+        <v>12.75959403514862</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>12.84848546981812</v>
+        <v>12.72607851028442</v>
       </c>
       <c r="C38" t="n">
-        <v>13.40675449371338</v>
+        <v>11.4494731426239</v>
       </c>
       <c r="D38" t="n">
-        <v>15.75949859619141</v>
+        <v>12.2522451877594</v>
       </c>
       <c r="E38" t="n">
-        <v>13.00619101524353</v>
+        <v>11.39671492576599</v>
       </c>
       <c r="F38" t="n">
-        <v>12.02793002128601</v>
+        <v>12.04792022705078</v>
       </c>
       <c r="G38" t="n">
-        <v>13.94117426872253</v>
+        <v>13.73998141288757</v>
       </c>
       <c r="H38" t="n">
-        <v>17.73049569129944</v>
+        <v>18.80403828620911</v>
       </c>
       <c r="I38" t="n">
-        <v>12.70472764968872</v>
+        <v>14.72197365760803</v>
       </c>
       <c r="J38" t="n">
-        <v>13.08956670761108</v>
+        <v>11.47441673278809</v>
       </c>
       <c r="K38" t="n">
-        <v>12.62036919593811</v>
+        <v>13.40818214416504</v>
       </c>
       <c r="L38" t="n">
-        <v>13.71351931095123</v>
+        <v>13.20210242271423</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>11.22369980812073</v>
+        <v>15.94044947624207</v>
       </c>
       <c r="C39" t="n">
-        <v>11.27709984779358</v>
+        <v>13.33455371856689</v>
       </c>
       <c r="D39" t="n">
-        <v>10.9982123374939</v>
+        <v>10.33524203300476</v>
       </c>
       <c r="E39" t="n">
-        <v>11.65936708450317</v>
+        <v>13.18809652328491</v>
       </c>
       <c r="F39" t="n">
-        <v>11.04593467712402</v>
+        <v>12.75842976570129</v>
       </c>
       <c r="G39" t="n">
-        <v>11.18878054618835</v>
+        <v>12.7200083732605</v>
       </c>
       <c r="H39" t="n">
-        <v>11.92013812065125</v>
+        <v>12.55573034286499</v>
       </c>
       <c r="I39" t="n">
-        <v>12.18292093276978</v>
+        <v>10.8825535774231</v>
       </c>
       <c r="J39" t="n">
-        <v>11.10318613052368</v>
+        <v>13.13756442070007</v>
       </c>
       <c r="K39" t="n">
-        <v>13.75860953330994</v>
+        <v>13.46962714195251</v>
       </c>
       <c r="L39" t="n">
-        <v>11.63579490184784</v>
+        <v>12.83222553730011</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>16.23895788192749</v>
+        <v>14.52443432807922</v>
       </c>
       <c r="C40" t="n">
-        <v>13.02434706687927</v>
+        <v>15.30260705947876</v>
       </c>
       <c r="D40" t="n">
-        <v>12.86267495155334</v>
+        <v>16.21514105796814</v>
       </c>
       <c r="E40" t="n">
-        <v>17.02461266517639</v>
+        <v>13.19220972061157</v>
       </c>
       <c r="F40" t="n">
-        <v>16.17860245704651</v>
+        <v>12.3590612411499</v>
       </c>
       <c r="G40" t="n">
-        <v>13.99701166152954</v>
+        <v>12.34228324890137</v>
       </c>
       <c r="H40" t="n">
-        <v>17.24501442909241</v>
+        <v>12.85570931434631</v>
       </c>
       <c r="I40" t="n">
-        <v>14.6506507396698</v>
+        <v>12.48598909378052</v>
       </c>
       <c r="J40" t="n">
-        <v>19.25188755989075</v>
+        <v>12.77763628959656</v>
       </c>
       <c r="K40" t="n">
-        <v>12.82392311096191</v>
+        <v>15.09630346298218</v>
       </c>
       <c r="L40" t="n">
-        <v>15.32976825237274</v>
+        <v>13.71513748168945</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>15.76427888870239</v>
+        <v>10.83357691764832</v>
       </c>
       <c r="C41" t="n">
-        <v>15.41799163818359</v>
+        <v>11.04766893386841</v>
       </c>
       <c r="D41" t="n">
-        <v>14.75249409675598</v>
+        <v>13.98432445526123</v>
       </c>
       <c r="E41" t="n">
-        <v>12.42594695091248</v>
+        <v>12.839350938797</v>
       </c>
       <c r="F41" t="n">
-        <v>11.72705221176147</v>
+        <v>15.61696124076843</v>
       </c>
       <c r="G41" t="n">
-        <v>14.79105925559998</v>
+        <v>11.31699395179749</v>
       </c>
       <c r="H41" t="n">
-        <v>11.36737990379333</v>
+        <v>10.56635999679565</v>
       </c>
       <c r="I41" t="n">
-        <v>13.23331904411316</v>
+        <v>11.25755763053894</v>
       </c>
       <c r="J41" t="n">
-        <v>11.85236525535583</v>
+        <v>11.63839483261108</v>
       </c>
       <c r="K41" t="n">
-        <v>16.41495609283447</v>
+        <v>11.34987044334412</v>
       </c>
       <c r="L41" t="n">
-        <v>13.77468433380127</v>
+        <v>12.04510593414307</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>13.11815857887268</v>
+        <v>12.08364486694336</v>
       </c>
       <c r="C42" t="n">
-        <v>12.38153505325317</v>
+        <v>11.51550984382629</v>
       </c>
       <c r="D42" t="n">
-        <v>12.14751410484314</v>
+        <v>11.24149870872498</v>
       </c>
       <c r="E42" t="n">
-        <v>15.11039280891418</v>
+        <v>11.40371584892273</v>
       </c>
       <c r="F42" t="n">
-        <v>13.58157134056091</v>
+        <v>13.5772979259491</v>
       </c>
       <c r="G42" t="n">
-        <v>14.24293947219849</v>
+        <v>11.6882700920105</v>
       </c>
       <c r="H42" t="n">
-        <v>13.2546067237854</v>
+        <v>12.0102550983429</v>
       </c>
       <c r="I42" t="n">
-        <v>20.05696797370911</v>
+        <v>12.08526492118835</v>
       </c>
       <c r="J42" t="n">
-        <v>12.1257643699646</v>
+        <v>11.54215025901794</v>
       </c>
       <c r="K42" t="n">
-        <v>12.76633906364441</v>
+        <v>11.78152871131897</v>
       </c>
       <c r="L42" t="n">
-        <v>13.87857894897461</v>
+        <v>11.89291362762451</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>16.86957883834839</v>
+        <v>12.30886077880859</v>
       </c>
       <c r="C43" t="n">
-        <v>12.85782814025879</v>
+        <v>16.46020102500916</v>
       </c>
       <c r="D43" t="n">
-        <v>12.67773652076721</v>
+        <v>12.35428476333618</v>
       </c>
       <c r="E43" t="n">
-        <v>13.65076780319214</v>
+        <v>13.09359741210938</v>
       </c>
       <c r="F43" t="n">
-        <v>17.20705127716064</v>
+        <v>11.44460105895996</v>
       </c>
       <c r="G43" t="n">
-        <v>12.54267311096191</v>
+        <v>13.26993894577026</v>
       </c>
       <c r="H43" t="n">
-        <v>14.70415830612183</v>
+        <v>11.60802841186523</v>
       </c>
       <c r="I43" t="n">
-        <v>15.68371534347534</v>
+        <v>12.6598014831543</v>
       </c>
       <c r="J43" t="n">
-        <v>12.47206211090088</v>
+        <v>12.97974514961243</v>
       </c>
       <c r="K43" t="n">
-        <v>13.31632900238037</v>
+        <v>14.88561415672302</v>
       </c>
       <c r="L43" t="n">
-        <v>14.19819004535675</v>
+        <v>13.10646731853485</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>16.04065370559692</v>
+        <v>11.68694424629211</v>
       </c>
       <c r="C44" t="n">
-        <v>14.41984820365906</v>
+        <v>14.03300285339355</v>
       </c>
       <c r="D44" t="n">
-        <v>13.32894468307495</v>
+        <v>12.94033741950989</v>
       </c>
       <c r="E44" t="n">
-        <v>16.88438534736633</v>
+        <v>14.974769115448</v>
       </c>
       <c r="F44" t="n">
-        <v>16.28989863395691</v>
+        <v>12.49633073806763</v>
       </c>
       <c r="G44" t="n">
-        <v>17.26598978042603</v>
+        <v>12.49726390838623</v>
       </c>
       <c r="H44" t="n">
-        <v>13.18188738822937</v>
+        <v>11.89562034606934</v>
       </c>
       <c r="I44" t="n">
-        <v>16.06329560279846</v>
+        <v>13.05229091644287</v>
       </c>
       <c r="J44" t="n">
-        <v>13.27770853042603</v>
+        <v>14.97833132743835</v>
       </c>
       <c r="K44" t="n">
-        <v>18.81547880172729</v>
+        <v>12.41984152793884</v>
       </c>
       <c r="L44" t="n">
-        <v>15.55680906772614</v>
+        <v>13.09747323989868</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>15.41560769081116</v>
+        <v>10.94561386108398</v>
       </c>
       <c r="C45" t="n">
-        <v>14.46057152748108</v>
+        <v>10.56815195083618</v>
       </c>
       <c r="D45" t="n">
-        <v>11.08270978927612</v>
+        <v>11.89603185653687</v>
       </c>
       <c r="E45" t="n">
-        <v>12.48028779029846</v>
+        <v>10.37860369682312</v>
       </c>
       <c r="F45" t="n">
-        <v>14.62396693229675</v>
+        <v>10.08441042900085</v>
       </c>
       <c r="G45" t="n">
-        <v>11.56150221824646</v>
+        <v>10.70943546295166</v>
       </c>
       <c r="H45" t="n">
-        <v>14.68144679069519</v>
+        <v>10.74572944641113</v>
       </c>
       <c r="I45" t="n">
-        <v>12.00500893592834</v>
+        <v>11.41163849830627</v>
       </c>
       <c r="J45" t="n">
-        <v>12.37168383598328</v>
+        <v>12.79250502586365</v>
       </c>
       <c r="K45" t="n">
-        <v>11.88249349594116</v>
+        <v>12.14600253105164</v>
       </c>
       <c r="L45" t="n">
-        <v>13.0565279006958</v>
+        <v>11.16781227588654</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>13.95569586753845</v>
+        <v>15.10887408256531</v>
       </c>
       <c r="C46" t="n">
-        <v>13.13200211524963</v>
+        <v>12.51083612442017</v>
       </c>
       <c r="D46" t="n">
-        <v>13.35230445861816</v>
+        <v>17.78771114349365</v>
       </c>
       <c r="E46" t="n">
-        <v>18.2845311164856</v>
+        <v>14.01196432113647</v>
       </c>
       <c r="F46" t="n">
-        <v>13.30839729309082</v>
+        <v>13.11928558349609</v>
       </c>
       <c r="G46" t="n">
-        <v>13.99373388290405</v>
+        <v>12.54847383499146</v>
       </c>
       <c r="H46" t="n">
-        <v>14.04592156410217</v>
+        <v>13.71544933319092</v>
       </c>
       <c r="I46" t="n">
-        <v>12.60420393943787</v>
+        <v>12.42792773246765</v>
       </c>
       <c r="J46" t="n">
-        <v>12.78333616256714</v>
+        <v>13.27031207084656</v>
       </c>
       <c r="K46" t="n">
-        <v>12.80665040016174</v>
+        <v>12.59302806854248</v>
       </c>
       <c r="L46" t="n">
-        <v>13.82667768001556</v>
+        <v>13.70938622951508</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>18.9769401550293</v>
+        <v>14.04957175254822</v>
       </c>
       <c r="C47" t="n">
-        <v>16.76723003387451</v>
+        <v>11.73635196685791</v>
       </c>
       <c r="D47" t="n">
-        <v>18.39172291755676</v>
+        <v>11.88461804389954</v>
       </c>
       <c r="E47" t="n">
-        <v>18.4068968296051</v>
+        <v>12.63889265060425</v>
       </c>
       <c r="F47" t="n">
-        <v>18.13807606697083</v>
+        <v>12.07912135124207</v>
       </c>
       <c r="G47" t="n">
-        <v>12.86636900901794</v>
+        <v>11.63795161247253</v>
       </c>
       <c r="H47" t="n">
-        <v>14.22650504112244</v>
+        <v>12.70693635940552</v>
       </c>
       <c r="I47" t="n">
-        <v>17.25862860679626</v>
+        <v>12.30691719055176</v>
       </c>
       <c r="J47" t="n">
-        <v>14.12941789627075</v>
+        <v>13.00639915466309</v>
       </c>
       <c r="K47" t="n">
-        <v>14.64209318161011</v>
+        <v>12.20800685882568</v>
       </c>
       <c r="L47" t="n">
-        <v>16.3803879737854</v>
+        <v>12.42547669410706</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>14.58101606369019</v>
+        <v>13.90479016304016</v>
       </c>
       <c r="C48" t="n">
-        <v>13.68549299240112</v>
+        <v>12.70997428894043</v>
       </c>
       <c r="D48" t="n">
-        <v>13.35167813301086</v>
+        <v>12.01167559623718</v>
       </c>
       <c r="E48" t="n">
-        <v>12.98742246627808</v>
+        <v>14.01839208602905</v>
       </c>
       <c r="F48" t="n">
-        <v>11.68920564651489</v>
+        <v>14.11323308944702</v>
       </c>
       <c r="G48" t="n">
-        <v>13.98217082023621</v>
+        <v>12.7500479221344</v>
       </c>
       <c r="H48" t="n">
-        <v>12.84246468544006</v>
+        <v>14.08130431175232</v>
       </c>
       <c r="I48" t="n">
-        <v>17.03150320053101</v>
+        <v>13.17009353637695</v>
       </c>
       <c r="J48" t="n">
-        <v>14.5096697807312</v>
+        <v>14.23229002952576</v>
       </c>
       <c r="K48" t="n">
-        <v>13.22830295562744</v>
+        <v>13.63601493835449</v>
       </c>
       <c r="L48" t="n">
-        <v>13.78889267444611</v>
+        <v>13.46278159618378</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>18.32037758827209</v>
+        <v>12.04321002960205</v>
       </c>
       <c r="C49" t="n">
-        <v>13.83616161346436</v>
+        <v>12.64131665229797</v>
       </c>
       <c r="D49" t="n">
-        <v>21.03488922119141</v>
+        <v>11.93496131896973</v>
       </c>
       <c r="E49" t="n">
-        <v>13.30531930923462</v>
+        <v>11.78015971183777</v>
       </c>
       <c r="F49" t="n">
-        <v>13.34700679779053</v>
+        <v>11.80536603927612</v>
       </c>
       <c r="G49" t="n">
-        <v>12.97001194953918</v>
+        <v>11.61028051376343</v>
       </c>
       <c r="H49" t="n">
-        <v>12.57408618927002</v>
+        <v>12.19877099990845</v>
       </c>
       <c r="I49" t="n">
-        <v>17.67586731910706</v>
+        <v>15.35539722442627</v>
       </c>
       <c r="J49" t="n">
-        <v>12.48484110832214</v>
+        <v>11.65507459640503</v>
       </c>
       <c r="K49" t="n">
-        <v>13.26381802558899</v>
+        <v>11.98498177528381</v>
       </c>
       <c r="L49" t="n">
-        <v>14.88123791217804</v>
+        <v>12.30095188617706</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>13.36100196838379</v>
+        <v>11.51712512969971</v>
       </c>
       <c r="C50" t="n">
-        <v>16.68449401855469</v>
+        <v>12.2990665435791</v>
       </c>
       <c r="D50" t="n">
-        <v>12.39301896095276</v>
+        <v>11.60705304145813</v>
       </c>
       <c r="E50" t="n">
-        <v>13.4784882068634</v>
+        <v>11.34425187110901</v>
       </c>
       <c r="F50" t="n">
-        <v>16.15880393981934</v>
+        <v>15.0076916217804</v>
       </c>
       <c r="G50" t="n">
-        <v>11.95067143440247</v>
+        <v>11.98659634590149</v>
       </c>
       <c r="H50" t="n">
-        <v>13.17744541168213</v>
+        <v>11.72052526473999</v>
       </c>
       <c r="I50" t="n">
-        <v>14.97943615913391</v>
+        <v>12.19371652603149</v>
       </c>
       <c r="J50" t="n">
-        <v>12.31367564201355</v>
+        <v>13.09625887870789</v>
       </c>
       <c r="K50" t="n">
-        <v>13.12241911888123</v>
+        <v>14.32400631904602</v>
       </c>
       <c r="L50" t="n">
-        <v>13.76194548606873</v>
+        <v>12.50962915420532</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12.5752260684967</v>
+        <v>11.20268583297729</v>
       </c>
       <c r="C51" t="n">
-        <v>14.74156188964844</v>
+        <v>10.57619643211365</v>
       </c>
       <c r="D51" t="n">
-        <v>12.25275278091431</v>
+        <v>11.21611499786377</v>
       </c>
       <c r="E51" t="n">
-        <v>11.97879672050476</v>
+        <v>11.86855840682983</v>
       </c>
       <c r="F51" t="n">
-        <v>13.90142822265625</v>
+        <v>11.95522260665894</v>
       </c>
       <c r="G51" t="n">
-        <v>11.84742379188538</v>
+        <v>11.20704674720764</v>
       </c>
       <c r="H51" t="n">
-        <v>11.79102826118469</v>
+        <v>10.4621729850769</v>
       </c>
       <c r="I51" t="n">
-        <v>11.68109822273254</v>
+        <v>10.86177682876587</v>
       </c>
       <c r="J51" t="n">
-        <v>12.74676775932312</v>
+        <v>10.78392338752747</v>
       </c>
       <c r="K51" t="n">
-        <v>12.57094788551331</v>
+        <v>11.76970887184143</v>
       </c>
       <c r="L51" t="n">
-        <v>12.60870316028595</v>
+        <v>11.19034070968628</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14.61884297370911</v>
+        <v>13.30738254547119</v>
       </c>
       <c r="C52" t="n">
-        <v>14.48793958187103</v>
+        <v>13.3626392364502</v>
       </c>
       <c r="D52" t="n">
-        <v>13.82932971477508</v>
+        <v>13.34950216293335</v>
       </c>
       <c r="E52" t="n">
-        <v>14.2034911775589</v>
+        <v>12.9794411945343</v>
       </c>
       <c r="F52" t="n">
-        <v>14.19016374111176</v>
+        <v>13.11391350269318</v>
       </c>
       <c r="G52" t="n">
-        <v>13.92707931041718</v>
+        <v>12.68504158973694</v>
       </c>
       <c r="H52" t="n">
-        <v>14.45317185878754</v>
+        <v>13.129551653862</v>
       </c>
       <c r="I52" t="n">
-        <v>14.41310934066772</v>
+        <v>13.40657855510712</v>
       </c>
       <c r="J52" t="n">
-        <v>13.64056283473968</v>
+        <v>12.95050756931305</v>
       </c>
       <c r="K52" t="n">
-        <v>13.66941504955292</v>
+        <v>13.17562967777252</v>
       </c>
       <c r="L52" t="n">
-        <v>14.14331055831909</v>
+        <v>13.14601876878739</v>
       </c>
     </row>
   </sheetData>
